--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,786 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>52</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16/09/2026 10:46</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12845d65bb9d361c3517dbaf962d99244308e0aa6cc00d3bde081cdd2ee05c6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>31</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16/09/2026 10:51</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ccb29ac08077664279644e78b378dbba5cd58fa5fbddc2ac2480fe19696fab7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>dd373a90048e1455cf2f9a2e152404967da30de0801da6fd0a809cfa1aedfb55</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>32</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ed4afa679fce09672830b0e3fbd79f15612dbc4bf47527c8de141ac0152aa293</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Orito</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:22</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3f56cec6284288662377c407fed8871c1058d6f935fb30ba1c27e159c6234bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fusagasuga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fusagasugá</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fusagasugá</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bc13325879fb3c206c95529fe1fe8ac8befcc67e9eff2a0297c7fe0ceb1d7614</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:16</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3f2392bb6d5d80e24c0d03ef2409ad757da70625370a98a8a735675887ae38f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:19</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>779ccde286f62d1d916cddc90e72a9001651ffd197fd975a0d9c156faaa3901f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Pablo De Borbur</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>c0f85d45d6c41186d3b524db9867c7b9bf0987bcffc0d4e3f9324e43ba0c90ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Paya</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Paya</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>e303bb636b441bf9cafe099b45d3a26e145ad3fa550af791a24623fc137b2516</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pisba</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pisba</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>e7c26648c548a9282f98e03a55bef2e915073421eae73835eed2cedb92d5857b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:22</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:31:33</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>fad5e3c91a2f933b13490639172d18ee38e4066569c780143ce4290ce40be470</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -421,7 +421,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15 17:31:33</t>
+          <t>2026-09-15 20:27:43</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1275,6 +1275,2086 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>fad5e3c91a2f933b13490639172d18ee38e4066569c780143ce4290ce40be470</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Acevedo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>46</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:38</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>b1a2182e0341443de9ddfa9ed5ee4a768c9ef9007a12a07cce18652aceb70041</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aipe</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dos</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>44</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:38</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1eaacc022d637142afafca294a1e44456593b84deee3af2f0f7a211fb54ad0ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Campoalegre</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cuatro</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:39</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>c0ffb8f9d49f8814d043db6db37465db1e45a5051f775f7143e53e5e3a934f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Isnos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:39</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>26a74988aeb5a16748bf8337f27200c7c20aa2da4057452d5f6a06e73df7a193</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Garzon</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>71</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:39</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3f375cd19777ca2f9c358e20a38d9092eacd8be861832fa58e504f207777d45d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Saladoblanco</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>40</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:39</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6ec872c0bfa6377e70551deba42150d051e76ee437bcebe757a8e951b4c01ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:43</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1b06282a7b0904da50c42746076a9d95b92ebbda08680dd4f55c956d8342d148</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:44</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>94ff1614bf747db1fb6e7e4900abddc4a8ad07716b8d429dfd00e73a833933b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>27</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:44</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>112a56515f131f21e704d9e65ec9ac8d57af1e08c7dd720e8f098db684c73dc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>21</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:44</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ce0a4b0c6e3ad7ea1685397bd75f2be88e253129c7be6138723cab37826bf41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>75a48e2215cae9ce435983af48dc25a9d384cd71b71af72d792ed740b3e0d253</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>22</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>d30752f3d78bd27e5369f06dbf063e869a32dea466cd3e32434f1c51469a465b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Soledad</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>c4a7aa857b27e0ff12207c190505970093d623e156aed566fb8ab2e68486d4d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ansermanuevo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Norte 5</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>caec76a5264a0ef22249705a5b587a9a0581b5353f8baf3b29d5e4afd511225a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Norte 3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>004f855e11308ae79edbf53209fed3967cb2e82893bdab37753e4e676f6ae4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>8dcc842867cc31baa55cb00bbdec5f5ef53dc1a5440fc8e831bcdc18cb170bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Caicedonia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>21</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>9847621337bd0a2ee2588346754d0ddf7c90cc2c12820fb88e2c40f86e8413ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Candelaria</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>d95cb50c2adb77e5b0aec4b79ce5b5efca1e9bd5c62bfdd5ae80fc32139b45ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Candelaria</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>3b1ffb6af373805f2ec2604b0d34e6eb02b9e64e34d50ce6fabcd45dc4adb312</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>El Aguila</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Norte 5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>12</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ec1d17327c4348d8961f237c32ab93b5c8edad892a38595573d799147933de73</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>El Aguila</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Norte 5</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>20002faa2fb4319d7d3f96ceff1b8ab962fad1c1efb9b92f2b9e1d9a1cf90d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>El Cairo</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>El Cairo 3</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>a99c502167d05352ade481a32f5c7bf0de7762362d87bcf52ace71644de7e81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>El Dovio</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Norte 2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>b25f77f03b8d9534df37fe10ea320f2634e2c92e2382d4cb0591f195aa31dbc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>La Union</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Norte 4</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>22</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>417857172546af4fb621679f35ce6b8bf7c7454dffd8e9087244869c308a9ee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>La Victoria</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Norte 4</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>18</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>222fa8c1ac1b49b751d24c41c69b2a5578a47b57706e18f8f24aaee49e45878e</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Obando</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Norte 4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>76e70a01232ccca06e26e42b897e888708170f811a0935d4d50b6fea98e1cc56</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Roldanillo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Norte 4</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:49</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>a8a34d191cab09127a6fc192ec4dbd8f9a2eb6b237dfe81d40e5ce383c71f0d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:49</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>0c17c00f19f0d8e0233398c5f5cf966e9bc5b88927a484f40e97994b7b920abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Toro</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Norte 4</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:49</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>a995c5290331061b411ed5acf15db2e068cbda5726451b40ea011ac8c0d6c3a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Trujillo</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>24</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:49</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>db64b0791f8af7544b7a440ac43baf9c114497ad45b23c6a699c4a8bb3530d8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>23</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:58</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>c41998c839de6177c3dd705df5748054aac4185e8c31f9288b27afe4cf6b4701</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>15</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16/09/2026 12:58</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:27:43</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>b72ad2816c86da550b5bd6a12a56f9a59174af70aac90437365778e603046b62</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-15 20:27:43</t>
+          <t>2026-09-15 23:07:18</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-15 23:07:18</t>
+          <t>2026-09-16 01:26:50</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,2476 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:55</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>d6b920335c154c3f97429df6cf44fda5d49324a46d1b6c0a3300f8f4be19a16f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>895853ee0310fd3f24f95be9764cdc8972f633d59256116d41e11a3f1eba1d7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Anza</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>c21fa95a5bc64b0e1fc76b3a798fedb0f615e0e0084aa879c8258950e3c9622a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>e7b6997a5dd5c90e4fe4d4dc1230a22bccdda39767aa1684a5b3c35e2bda35ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>San Andrés De Cuerquia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>39b2438c5642093eb3acbf86f2eddca9aba1c7efab3980234dc445e0c0e0bffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>84e49988b50e2e7f560a1bb5cfd33bc0bca96dc4383bc20f3a73a22d12e4efbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3ba8f8686f8df0e3a7039327aee86539bc3b91c22d1957354b1283bef1afd71a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Don Matías</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Don Matías</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>09fddd2fa2834b96455614b0b9276e587f4311c7bfa49ffe19b9dfb31de90aa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>29e63b166b82eccf0b2917174bdac517c4be305e6c28399176d88c8fbe8419e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>7ceda1feb6202deac8cf9aabccf44418741604e310a443d0c9d336d31e3568f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>798a6095fe5c6b02b302054ae12d88503b33509c9633586f501b7a20d4a200e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>35ecc97c0baa74fb383d0e703fc12de1d3db1b2f78b9af89aca5c94204101a65</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>a25679f179ec9b06eda319fdfc80dd7053da611f5eb56de7f95604d20d52ddd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dd8cd43717c7b96bf1eb63a0d147b6f48ed847205b3e9534bc342fe2f0fb6f2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Educación artística - artes escénicas</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:56</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>c087015d6b12bfc64a4af5dc64eed3af4326c2d9110f194b7118261d92877689</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Puerto Berrío</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Puerto Berrio</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:57</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>701d6044f2033cf2dae626af3a3ee691705b760e4dcfb45177eb9b41220bfc3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:57</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>9417f802a44d3904feb1ab80c0106827023207d3ef5b2c57f655fd706f023b50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:57</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>989edab9f11ff4d2bf044f32a8150d3460e156839c133269c63bc304774033bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:57</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>dfa52648dcabefa15a6eaa49f5317946d6e202191858757a5c62fb974316941b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:57</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>c0cac71c94b22ca51912b921abfae1435d8b09aaf324c1175ae6068996b0bbb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>19/09/2026 11:59</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>d100e69d1b3f07e0fe0bdfd65e495a4f2ebc18c52218f8554f47f02b2e175843</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Caparrapi</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bajo Magdalena</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>9</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>f8b50ff1560a9dd3725c3f5cdb0725c05a21d97b1f65154892e34bdbb3a599d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Quebradanegra</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gualiva</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2ae6d2042632df5fc9061580afe210d07db13877a18423f1a94e4f0e00779170</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Caqueza</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>5dc36fbe5574ead74fcffaef19803e6bda0e411c7c8ced2023dd51da2a364b3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Guayabetal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>541fadca6d38945cffd74e0055598d38019ffd4f4bbe60ffc11838b6b12fb84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Yacopi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yacopi</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>725fa71e258c85d9de6e704fffa34bed445ae58220c17ea7d9401262e6b927c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yacopi</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yacopi</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>7af9862de80667ea5add1cc818987e366c1af81a295472161e7f2c6d379765e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Simijaca</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ubate</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6b0ec8f102c13d5e095b36bb17d26bc86bd60cc283183e9d02bd242db720c034</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Villeta</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Gualiva</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>310f9c0772b59c325dfc6a5af089a816f116aa456544c1582bfb432d021fa783</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Aguazul</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>b25f692f849cdc1e8ce7085f87f6428db3d6bfc4a829314948a054cb0e96ff93</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>de1539b35e9f8c426af85ebe5f5fa64ba322672c5505084005be60fa02236033</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:04</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>a7342b9bc24427d7bdf785172d60c37c533a1fae2b332ca081b6c92207b10e20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:04</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>558809424b13aa6ebb8069f6ceb1ccbf8549cb7c18b4db2c902a978b3d5b7b9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:05</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>223708bbae8c55bfbe7f9ab12b504e8b6c511c44423c702cf3501c494ffee6dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:06</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>a953b18639886b54e3baade6fac75bdcea29517128777ebe0f02bbbafb866a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:06</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>5d9478bf54d32fd1d39608d0d9ef59a69fe70ac25e5b48f84d660b8dd5bee890</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DosQuebradas</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:09</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>da222ddde6c50ba1afc22e37aac2591274572db16e6e6e9112da0515ec5f2d71</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Puerto Wilches</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Puerto Wilches</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>19/09/2026 12:13</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:42:51</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>940c21b4d7920a6b33db202df952fe5ba174bf807844f6f00ab73c463d8c3cb5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-18 17:42:51</t>
+          <t>2026-09-18 19:59:26</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-18 19:59:26</t>
+          <t>2026-09-18 22:29:59</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-18 22:29:59</t>
+          <t>2026-09-19 00:34:10</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,3256 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Alpujarra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SurOriente</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>f4bbfa45472c6256742888ac206cdd0f20d1fa5f6febe276a7fc64158de6d73b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Armero</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8f557664500055167463dff8ee7d33b38951f884aab654cf0ac3955e956b2803</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8603e0ddc0ef1e9ce491a7075dea6427e62a7fc8999314d9abc85bf4da4af4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Falan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>f70a59993c99d10ffbd43a0c23c44d16ab2f4f7db919b64f7758c4a420486a8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Honda</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>7a6e47929e3964485a89e297cea2961f8e6181da8c1a26e95e80c40f3a81a94d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Natagaima</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>71c9c49a536b8855238e3537bdd201276d858ed98e50f1c1923bf595716f485a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ataco</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>82ae9b7e6e14e9b1f707416392ab9cc0606f9c614ab096d1bfb09fd3c8069672</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chaparral</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>09eb6fbeeb7bf89f73fa1d60bd81d21e9d76ed25a1b3318fe3d6adbe26617490</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Libano</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nevados</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>a41bca5a3394597638d5f2ab83cef3b23a4da3a6ab8efba10d644b2a0a8f0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Honda</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0bd1ad8ae43a2f3828d4323e94a373d9d7ff9d93dda1d9cd6f07f09f398abe6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ataco</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>12e317bccd9338ebcdcedb9391dac4557c5fc2ebd81a8e54619f567f6397887d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Casabianca</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nevados</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>82c2a38bc39b787ddcb3159ac2ae6a691f574dd317f24e82d64d21fa30081348</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cunday</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ffc75cf5da7fb195fe273808b8618c047bab1dabcd49960dac0ff162a37a7a2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dolores</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SurOriente</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>53b9f18ebbe09af348ca16d84f6ce18221fcacb8ab7e524718d12989369f9635</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>18df5bafe25f5a66cb109bfeb81e6e613a255c04ad3137bd60b6a496219b9afa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Murillo</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nevados</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>11</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>16a69bc23375a100debec8e4727fd23dad44a08692bc8a341604678e59fde76c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rioblanco</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bbc5f1471954920ed724d5a7e3e7bd302b6263595782756cc88823c392ac19b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>19812da55a3efd687d69b8fac60d15678f16df47dcf72c4d071a5b96a5cfa034</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2c9532e6302e5d25c91f2f1b280d0bb1669aa2831ec812e463123abd7a6dd190</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ortega</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>4001a06a149de3c7799d9747e7bbb7a5b3eede8e3e6488bf4f7155f36357deee</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ortega</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>262c0409d5fbece6edebed3b32ec5b34e88405af6d19def18366bb79d8521a2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4ca6f4796a961374c1758d351d5a8886e06f7ba7fb2d217a77689db3aec73954</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>8cdc476a5ec5723a4a81a71b07795a4b2523fb7c7310a1a1c2c25ccd87bcc40a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Melgar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>850ea132e2e79459a4ff0ae285ff719ca01a20bf98e5d76b0eecf512c5a7024e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ortega</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>46c35f42e24c791141b69adb8f02d04b839d1a59257d9c3ab730106d4e3f8017</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dolores</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SurOriente</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:31</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6e131132d5d8448c4f21cd533000662d0b4264eb3d9fe5cb2e654231da907d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>21</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:33</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>75c9de7dc30968a062517bc08ba2f928216103baee5ea86b3ea6124ed2b4dff5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2227f0c182fa39182659434869c89fb7a73e4c76deb5a3a8025754d5c23a8a0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>19</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>83de6f2ad5465f7f4794605fc0a68ed881713517bbbb759611dc2ebb0f9158cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>e73f99d3d10b0b2cad5f63e0f138525c0feffad8533353bc2853182a2caff4f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>San Cristobal</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>11</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>4ba78607b907f8b5351c956a5386778fd2aae65b2576b51524afea9fe87b3150</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>San Cristobal</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>13</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>14bc60c606181c999ffb62a6e117506c7bbba11a1176b8e109e4e527b2b98ca5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Usme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ad02accb0532c0c5cc2cdac2ed1badafed296b85d7497321cc43c40f15e25f57</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tunjuelito</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>12fcb3caf7eef4d45862fee2d8a0c5d2941a9faf0952500210e92ce6b37fa065</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ac11cce32b2e94c144de47a393204cd0c692adaeaa92a1aacb7a50e8211b9574</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>31</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>f2ae1df6c272cea7a1eb4a7d6c8023c0e3be6cb262bce1a43db368d7b13558f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>8be35823ad2c5b913ab3d96010681e16d1918cd158d79c4812fed2b6dd1222d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>13</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>a828c26ba6f79df3db9c68ac3e4f88333cc3d396d3f1220f3e373bf7fe9836ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Engativa</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>25</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:34</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>dd8638e7a6bbdea55fe18bb2736c29b13472e08e0c93835137e62e2ecb2fe105</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:35</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>d69d8e2423e834b03188b99371042e835b91bfcab2255cc079a31eb5cf19872f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:35</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2e46f6c1cbd4ac05e4f461d9376c1e8bec67c8e0a2d253c65f9494e4e374f5cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sumapaz</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>13</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:35</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>6a901c441e170f2776054832a9a00a697144711feab1b86ff3b774914f318d76</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Repelón</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Repelón</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>14</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5ed25d377829300a8aede06e7e5ce1427149bb7c29c445bb4e2d2f98c2e276ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Manatí</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Manatí</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>16</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ad51a6cdcc3ecf62a54e4938aae6869de3988729ace862019c7bf05f4d431b04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sabanagrande</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sabanagrande</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>17</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>a4413ea852fa9b714ba4423c2e0625c27fabd46b5946a5b4af8d0506cea22ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Palmar De Varela</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Palmar de Varela</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0195f7e40e7e95085b62c65625d823970d21d4d679d18fb69761e4b4e7273488</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ponedera</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ponedera</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>69b444025d95f834c37febf621ada9e2e5b41b88f228a8e753e913e6f65c5e91</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Usiacurí</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Usiacurí</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>7bcb132a4d7844b0a8b5d67d3e4b1370dd91ab522da7e6fa3f73d5d316ba58ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>72ec3cc541851e9bc2663679e1974a2f76cd6c6d2fd8216b93c57f806162a765</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>22/09/2026 16:37</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:30:03</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>96fecf8410279e5da7a1d4d5d7ba10c142dcef2db4686f1223e23f9535673826</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-21 22:30:03</t>
+          <t>2026-09-22 01:05:38</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,266 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>San Sebastian</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>San Sebastian</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:46:19</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4ac754176ab5b22990f6aa9474ffebe4930c23982a8cd1a3f585cf804769e206</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:46:19</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>f34bbd63f524ac0b870db2618b1d4925d06c4e0065913ba31d00bff68981737a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:33</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:46:19</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ae2e8182489b42b75308a95e4755e51c859bfc134508830f8a9e7a707023e0be</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:42</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:46:19</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5a5d62bc6ff82b60a287fcd11ce7b65a89cbfd3dacdebb45527e3241ce18030f</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,17 +413,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:46:19</t>
+          <t>2026-09-23 19:59:42</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:46:19</t>
+          <t>2026-09-23 19:59:42</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-23 16:46:19</t>
+          <t>2026-09-23 19:59:42</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,26 +735,4056 @@
         </is>
       </c>
       <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:42</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5a5d62bc6ff82b60a287fcd11ce7b65a89cbfd3dacdebb45527e3241ce18030f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>904f20ac8192d3a81b554a00803ce7f499c18b0ea5cda9fb129ec48150435db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>46</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8d65aa97dd3048fd8aa4f1fd56231d2555e8945c94a62a7395550f5ba781d2a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5f06c0c9076ffb81d96e6f1fd119f824551a14bab32f80b5e33f7d74a12c4d7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>48</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:48</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>a3b3e5ea2515021e161c58c7dbff9eac0d16596c5422ec7d3ee720cc8009ecd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>27</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:48</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4c4220d3ae9c05e3e42d8a2ec804e8341f62283793d0518e8fcf2efc134c7a78</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:48</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>18d5cf43e9ac73c73170afc5d8192163abd0643d7592bfd30022e6daeccfa3ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Consaca</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:51</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>7ffeab5d693f14adc9afd15e39ea2a2b5365ed3159bc74f2e917b15e09d1376b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:51</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>a256e37a22ba68f23a36799f6be674567b841a95b8af5e5b509298bfdeafb2ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Iles</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>9c65cd12f049f98ee0cc2a067919e0b9bc8823b54efb9f525a82ac57df35ae25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>La Cruz</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>c9f3e1fa938b41391ff0664a4cfa79a1d88702fa59f51310e136db059e2abedf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>La Llanada</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>c19310b46ee38f732baa9e48cd027bac63436b9f0ea6be9d8a35c96261ec9d01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>La Union</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>7471a5c1a14929fadb4f8c9e59468c8fd66708beea83035c990068babb12b1bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Leiva</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>c302431a38affe712d288719a84360a3886bfe8edef607e0dcef61c1542783d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>21733c0f59525016b3bec4efb563fc78b70b25e096057a68639ded272a423dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>c36321723cd8c7a8d624436eca122a08396f959cc6cd8ca95373a4b6915a0f72</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Potosi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>67fdeae839b0c7d43fd89dbcc78253828308619d15398d6e95c38c8d4e5ccf0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sapuyes</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>405a2054350375260adba3d8d1e2aab93acc46f0de62714c2efc5fa3419fef9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Taminango</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>24906ced3c6ff3b0d6a09c54de103ef2f6a7bd6d92a8a4b940bf43670b71c3b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tuquerres</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:52</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4f4759601b28a57db09e185f3f0419fe367bc91919c10490142f5548f4104195</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Samaniego</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>492f3b581c4fc9a548bb4b11d6f6efbfd3a5587adc56b485d480ee13cdf68011</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>7f207fbb1b1542ac02ac1f7483b80b9f73a6577c12ca71eeba66b3a19a176b0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Centro Occidente</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>12</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>33ed8b925241a8190c64f226d320890e843c5ffc8229ce816655a2f663558af2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Puerres</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>464382b361ee5c4304723f2829d2f720c91059cc6e13fd1908c090f031114f64</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Leiva</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>95c2ff39019d9006e1f21f956321b4c239a064588cb8ba9a62dba4fb1779e2c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Taminango</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>13</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>8cc46797e9f8284e27eb70bb6a8f731d4c5484947b8d7e3976c0dcf0f52266dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>El Tablon De Gomez</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>10f0d6b20dd784d78a55ce402bfc154e31dae250e9407fc31b1cfc543f7f852a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Leiva</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>24/09/2026 11:53</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2769e551eaa0158604c2e61049e5733a99e339093538757d461f3bc4a21fb0aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Aguazul</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1c96e1a44ed009fbd4e2452d4a16470ed536b40956dca55ff573f0daec9edcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Maní</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>72d564e2eff2b1c16d26a4cdb5cd35cb831aeac8503569c2e15ceb7432ba98c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nunchía</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>12bd7caa1cdb12d406df2eb848bb53c23189691ef5ed2b7707e152a8381fe030</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Paz De Ariporo</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>e15c850b1a94b269bcbb4162a25dcbb12b0b1d3ae42a45de2e48c155bbe709a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pore</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>a96f4665313da49de3a7e9a1f2ae95ba5d4937f6c48e2d9dc0134c0ba5b3bddc</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tauramena</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>e48609a817e3196ee2663197f003bc3e4f86196eff972ab21911bd176bbe2888</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6b977f9b7304f4af8b0c4db3128695f82c5fb0d85c4aafcad3155b6b7b140bf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3d885c5d7ac4f7a814c5f5feb8bda97df731f38ddb486ed17ca122d5f1a4c606</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Villanueva</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>fbf1a392d80afb31e841f0e58be5fffdad070e1ad06d1ea19eb65d15c94dc5d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Aguazul</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8b13f3398d20157b6bb3cb32a1303f0ebde49234f1d8060e17390bcc229d2f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>28</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>c503e6d1545971d55f731d5cd9a384ad15a91a7a4fad0575dd9429bfc11c8aee</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>14</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ce25289ba2cf2ad2fa3d78c1af854d7b6604ef2e1e84ff5c997060d4e377b916</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>17</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3186356b023ed6b08128aab555e06f5a7caebc3dc7ab617f82ff8fc3b1772208</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chiquinquirá</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>15</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>79d8aa1b08303fac20860e047711e013a7c5a72ed5f14015445b7024639c2d50</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tibasosa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Sugamuxi</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>27</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>74404e60aff34422ceea7d014a7585882d089b56642e07062f00b71634075abf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Otanche</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>25</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>e293c033004a9fa4dc2294b4a3b052e04988e2c25e93b6860d1946b7f49f9b0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>El Espino</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Gutierrez</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>27</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>f495093a6ba52cbdf24a1f6c7da1e246378fa2939dad90f617fdc6e5805b8d62</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ventaquemada</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>31</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>f06f315bfcee2fd737bbfa72aae61a44144cac44ec0168f6932d015529731910</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Macanal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Neira</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>28</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:13</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>d461d50036b66f7df4382c462e2c7c9d4d9a165a926c6154878d54ddbf53b9f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Facatativa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Facatativá</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Facatativá</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>64</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:14</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1c578991678d134e5043101ce5485264f588af6336c686e81e0f5254b5c06bcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Catatumbo 7</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3655714b36e2a099939e29efc5160d6ff2d7336e01c15d459e2f1155f36f4dcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Catatumbo 7</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>14</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>3bd5df1ec0999882b8140c268bde3d7cf59d1c7d6c168594269f05182e756082</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Catatumbo 7</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>c0982d2f48b077de35e7e9834a89fff70ea818b6e7caf1081776502424692122</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Catatumbo 7</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>12</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>167b36bc7e4390b42f62f6306b4537c9a10cc616828c824d322690a2278ae630</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Catatumbo 9</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>49d1d3d4793b339f003f5f40f6c5ac28e66695e80496103bbe08aba5e31f1a17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>La Playa</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Catatumbo 10</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>a61b180571e87e196306264ff8d0a10ae3b2549e9efe611f0d597e86c12823a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>La Playa</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Catatumbo 10</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>13</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:18</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>275a192fa38efdb732d72f6cf7409a90217f0242205e47d6c05dc850a6949d49</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Lourdes</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>d199223ef69242e384baefcd8892f48ae73a941638502d5b3fa3d15da51c35c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sardinata</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Catatumbo 11</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>9</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>b1e0952becb2133db473042b09ae479da84464ad9354a409c16b5a3eb27713d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sardinata</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Catatumbo 11</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>4e6a98e0e9e58b21d52709ad3657a06e271d5a5185f3ad62c6dc83a1dcd57e79</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sardinata</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Catatumbo 11</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>13</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2a5a1ad697de5ff2b7559b854cc94fb23883250a30dd8c389bbacf30dfb897f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sardinata</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Catatumbo 11</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>24/09/2026 11:42</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-09-23 16:46:19</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>5a5d62bc6ff82b60a287fcd11ce7b65a89cbfd3dacdebb45527e3241ce18030f</t>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>fe64585c3c5ffb6052cfa469b9b640bcc16c1b3f1ffd63336a9f43ff15d96193</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Teorama</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Catatumbo 8</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>8</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>83a9eedba0be1773286da4332df09234c4e94b94e3a8cc3f6dbb3af0a60fae14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>4</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>3d5046fc2e109fc9497d9bb3a78cb25c654b11ce1e0dc7d7790e20b37202bb21</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>24/09/2026 13:19</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-09-23 19:59:42</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>e76d871f7860bd2377bf559fd76ca330500c42eefcbbd3c9844083f756f002f8</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:42</t>
+          <t>2026-09-23 22:53:51</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-23 22:53:51</t>
+          <t>2026-09-24 01:12:35</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,2736 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:34</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5fa2e9ca6932ba1fdda0653255b4144f5ada7203896e439d32752944128a0e2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>San Cristobal</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:34</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8dcf623fe8350fb2c30e08992ac1975ada6686878f7b5287ab88db8db95dfe50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:35</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3b99c055af966a0367ca5b190ad16abeade0a11d0a04efef3e9dc5d2b01a6657</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6f602d7e6bfa5dacd0c69842766b9a598c51932e2b6831327ff2da97cf6385b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fontibon</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:36</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>601ad706818bf448aaa012c74143000ffb59befd15152bd73056e1bca0edbdee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>La Candelaria</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>18</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:37</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6b7c7a945fb9d73ad193e2e2f70bc846f136737bf6d6bf778108a38abb331fb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rafael Uribe Uribe</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:37</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>72208d2694ae85621b67e1cc8daccfd324149d8e5f3605a7544317a0cb1bd9c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>32</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:40</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3ddf3ce99266d2e4d25706ad82e947fae923d40b2645cc8651ad23468aa6a8ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Guaca</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Garcia Rovira</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>8444b324476059481269499ebc1518ef56500d56c7e9080a4a3243b937ce22c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>El Carmen De Chucuri</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>El Carmen de Chucuri</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>30</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>251cf43746123907483b4f6a07f87a4c508061b19b9288e247a957be8d499c32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0c9c97585275aab59804e5399a2f96b2ecd0606eb124e6da1ee4cfbfb092c1a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>29</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>8545ed53eff0ef95542cdcccc006fca295ce6c10673421136a19d4a142b9851b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jesus Maria</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Jesus Maria</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>36</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>9f2b125214b6c26a7e9db72818d2dcf7b95c7f1cd61e6269a9623ae74b13d454</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Puerto Wilches</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Puerto Wilches</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>34</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>05e1217a26775d01e6887784de8cd706f8da259c7a1ed6c8d41b64ed8b1410d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>31</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2f2bda99f2f2909775fd138e75c2c0e02ad2a547b8c865546dd177791ad4ac46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Santa Helena Del Opon</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Santa Helena del Opon</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>295e45c431c02cb7a0b44e14cf3ef490fcbc39bf1166b2f4bed4c18113772ac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Santa Helena Del Opon</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Santa Helena del Opon</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>35</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>891fd1b2a421ce4cb5dac8b4558bc5a63540e28436a403b5c8bdd112cc70afa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Charala</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Guaneta</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>34</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>f6d716624ad9c7d396006d0162b339ee0e81b4bdacbd9a625f308d8b137f42fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Barbosa</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>44</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>75a7d517da5e61627f04b3ec6bcc472c3949b3468825ef7b8b6347a7a268da0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Barbosa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>22</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6e580d6ef1c695c132cd0560a6949fc022c041d09c82418724d6654b6c416780</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Landazuri</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Landazuri</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>39</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>d9d47970998403cd9f84a3326bd36a6afb1a2cc5cca216c842ba4b15ebf768f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>9e40cb02cacab57ef2659a55f4ba39967512544c22c6f396e33d04ec82d45faf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Contratacion</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Comunera</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>be71aa23ee20e53e8a37b498e0940b944a7eadd0bfb04ee5e444b250be83c212</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Vicente De Chucuri</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>23</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:49</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bb439a04233e29503377e95f5af29b1d716de512be821668aa0f43c180c04934</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>37</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>d410815c66aa6ac19db54ccbd3cbbce9fb0a6551c54612fb809735accebe7781</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Puerto Wilches</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Puerto Wilches</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>9378cb11e6ec3f1be7b00038bc7757a591f16d5f61e4bed573d231c11d0b0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>El Playon</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>El Playon</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>13</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2e08fa92c8fc7476b5f759cfab7dab763e9ab52f6203bc9b578acb277f676d87</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Betulia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>27</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>bf1dfaef831555b7aa3a2459d65603defa0b014e1bad283a4154d19419cc577a</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>El Carmen De Chucuri</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>El Carmen de Chucuri</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>28</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ce56bf16eec74f75888f3c6c20f806f69cff09dc6453e2d0658423d9f9901784</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cimitarra</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cimitarra</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>33</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>39d3cc46a05a150941eac14fe4279a3c3d603a1ec8df474b498ff5661f12a8eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>La Belleza</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>34</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>fadca53d1c99036397b801478a9c535fe61c745d402f46960f26c536497a48ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Vicente De Chucuri</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>32</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>45cced2a34551c4c7a2284b5f54e097a9a3226cb6e9cc02c1abc78fcaff53ca7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Santa Helena Del Opon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Santa Helena del Opon</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>34</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>69030c110249e83fda425fc57944213f9c0717c03b77bc873453e13c9f71cd00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>28</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>ba2ca8fa5e675f1f10060b01a2a30aedf76b13d4e0a3f6311a276c2c6ff8a883</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>El Guacamayo</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Comunera</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>82</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>043fcb1950d5c859b9ad111fdf8a8af756607b4c6b1ad8bec94652b14182641e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cimitarra</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cimitarra</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>12</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>8dc9944d3bd44431fc9fb8063d84858a0ef2bed373e42e5cb2e53a687f6bb40a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Vicente De Chucuri</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ec3fbd62eb95edba1c9bb3ee3544b186f3f635b85a3bbd8f39a471a22c9efe00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Garcia Rovira</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>26</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>51068d8e4427f81b6f79cdeb5441b189ed0c6ee56ad694e291ae009287dedfa3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Vicente De Chucuri</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>25</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>25/09/2026 08:51</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0e5a98282e28846b2ab4f0451f5da88962d6d76dc690ba015b520ad8ad6aada3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>66</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:08</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>16937eb360be757361a3dc5185080225fd4fd6926c376360824d64443bb73c23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>36</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:09</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>728da1da7bc4348481719d740ba563a3975d3d08b20d5e24b20af86eb656f99e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>64</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>25/09/2026 09:09</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-09-24 23:14:02</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>38ea307d86fa14e81eb0b448c231a680673545624ae629fa6141ba9394a3b1ba</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,1046 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ciencias económicas y políticas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:52</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>170fa1bd62c11c16a6568b1fd6534dcfaaf8e6628d7ab6cb64d1b6a0ef35bb7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:52</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>78ff743bc25848e05b88e9543c12a457f501f5b91b04a949662b4b7390aa4b64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:53</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>73e16155e3c9e3e7449329eab2b960cecdeaccc68a9d302ca0d234d9a923e831</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:54</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>371dc0beb5eb58d620cd1db76e109a50cb6ae3ad5feb6e59a3d8d4775a10ee91</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:58</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1c8f36331ec0311f7912a0018f17d248f8b63c67de1a291972dc5601b2ee7f71</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bajo Occidente</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>58eba1e1cc285a006fcd50926a84b15858094e8f2959bef9239429573f5f362e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1379cb3c9906b7849ecf4f604676e0d254155e6ee2924ee378ebac9978e421c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bajo Occidente</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0b04b106e3076ae42820dc8ff204887c00887f7bcf2eec6ab279a8b2764c8c99</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Alto Oriente</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>55c64627429dba5a902e90dbccd755586cb1c32d9a204efda7539a7ef106dc3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Alto Oriente</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>39be2831b78c5352d17a98e68f09ed9be62096a506a15cfc20980e5d508d5d24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>80ff1e1c1b1942ee1439710b96befddab13df9e4387a56e99143184f9ae3ee30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Supía</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Alto Occidente</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bdc7a56b636e94d6e9ef0a4cdf669f280380b958203c05bd7905e32d5e590bde</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>d72846a1309fb6776dcead8aed52f3e74708acf29228ce9e26b1a23b04af8d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bajo Occidente</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>a143d380656f5951f37e078d621448507f73a1805a774659298c1574fe271b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Norcasia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>47bae025b9a304fd046edc8d5f50728f07cb2bb7673d678d68bfa3f0aba3dcb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Villamaría</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de Aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>29/09/2026 15:59</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-28 21:21:15</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dd82272373b461de2f7b733bf0647388cbf42fb866dc2e76b57d4b01b52d9448</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-28 21:21:15</t>
+          <t>2026-09-29 01:10:33</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,4751 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>180538300acea39b1c9eade0985034e2d50814e01b09c7afe7e52289d7fceeee</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>La Macarena</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Zona 8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3ae8449173adabf9ee3651c4b64e239ca8f49860c24786f161a9eaededde7422</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mapiripan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Zona 4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>d34c7322fc9b3dfbd7b27d213c1883fd2d123193bb356a71e53dc6ea1d08cd32</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Puerto Gaitan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7acdf2fb7f5c9b653e9c9a3e81153046715c3106f11a48d4b9badf7422c07d9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Puerto Lleras</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Zona 4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>71887774b02f59c58edaddaf37e091662bfd89e0945c499fc9196e53c1833c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Puerto Lopez</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8a3cc5c3ff176ba87d9b6c80ae6c2f8dec84a4209444007dfd054bcfa54ad33b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Zona 4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>de8f8cbfb470598a48e1757938ebec6354b8797e9adea92da12f4e51b862f265</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Carlos De Guaroa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Zona 5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:33</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5c207d45229be6e9dd8317fe6c6e5750d2d2de5275f0fbb80125db87d60f1b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Vistahermosa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Zona 2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>59bae98eda294858fa07b532a140a269eadaaa5fe2d7c474fbd8cf316efe853c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:34</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3d7933c74a99f6ba8fda742c9de31fa169bda791666692c89069017391ff714e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:34</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3ea4c9efd79ed7addda54361794f18f4c371bb984ba3b0c0980a599e39b80ea1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>21</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:34</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>f80ec54d85a47c6f024fa5515f187a13cd04cbded3904eabce4ab77991a80452</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:34</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>b338626024aed488169e25543bc58f14075f3e22bc54aed8a0998f543656b2b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>14</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:35</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>b4cd746252ce5dc98de3e6f2b3def98ab698dfe93146435b238575dc233f328f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:38</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>cbb96e15a0047f10e3049bb1302a77932eb6ff627d3ce07b395a08d619238d1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:38</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>361e2b91e03795315649a6fb75820ee75d4fcd6dfc319d31fb6fb3e2f8b6600e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:39</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>9f00b474efa3dc87b4be22eb063b17cc299643bd6dca26c59be1f50219c414ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>21</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:39</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>82025f065cdcfbc8e3b3fac2883a90cb7eeb3fdea49309357c6bd9c18072d8cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cienaga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ciénaga</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Urbana y Rural Plana</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:41</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>9877882425bf659cb1346e7009967ba3bcb79c23e2eba705c879e37d746707d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cienaga</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ciénaga</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Urbana y Rural Plana</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>50</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:41</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>d65f86622e557593964333492a10be3f6003d9e1b20f5989c451ea04440353c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Cienaga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ciénaga</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Urbana y Rural Plana</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>02/10/2026 10:41</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>11a3d2d27fc87356d8a9e6db2cb102104d3b73cbad40f2fde70e05633ab47ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>681bc22a3f81a0b95825fa5c57bbdca5f3d9cd3d52e246efbc7527746a49af3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>San Cristobal</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>bbafd3cb1e044ec9f638e1962feda18d01eb35c36030b139917b6c02e8bdbff6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Usme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3f75294261cb4a6ad931d937f5790ef767aac162d7279411c379d4e08a1d4816</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Usme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>dd4a82f66cc37eeec65b03bf3f028a671fdcb1cb502ff5da00ff7006d3653b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Usme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>9a77cdcaa992bb59a7edce04a902eb0a200235e8c983b3eea6808de9d86ce4b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Usme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>9302bac47b05b9ee35579f3ceb5405930ad22deaaca179ee9d6969b042bb4982</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Usme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ada95d3a5d3d7a04838a8fbffe210c40272e20881b9fa53f7e2d798929d9575b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:34</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>a6dea697a740b7b49ccaa5545b19a78566656ef7cce151b8ea3da2a608e77549</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:35</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>7c2fd1553e33fa28d530dbfc22aa6ef7e595e6d1b585b896b8e27ece9d333672</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bosa</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:35</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>e56e1519be51da4f41a7062dfeeccecba42b6cf3c031cc75ed4b7f3b84ef27b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:35</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>36e366760762f96b11aa363897ca6747cc33e7921118ee65e166abc528ab31ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Engativa</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:35</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>a34700f9d39346bc4cc1ea4c29a46ea90dbdbcd261891e963f8048592aa0161a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:35</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>44a773c989be3e4b6c5ec7539f08616a2111f48f49ba9756664beb2aa4581610</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sumapaz</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>12</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:35</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>862231b440970660652d9f8c7a8c42ffe184e7fd82d6980425139f12747c488a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:39</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0e12e439b4e9657cc45898b1ea36aafa87c5100989126a590e953e080f537308</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nunchía</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>fe736bede357eb94c7a7f1c34c84c6dbac1fe71c3db830fc78422da8d80179c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Trinidad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>d83abe99d9c2035949d3914d9ed9cc2daabe75bb1968e873fbe6704c10e416f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Paz De Ariporo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>39361d8dc1ade26b382c1b0cb3fdcda6dc96bda04d8cc216bdc6dc57d1f79fe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Aguazul</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>cefe4c34483a56549a6f1ec9564788eb2914da9a923860c5eaa41c0e9b3c5b01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:47</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5e3c3501087ed5c7ce71f7869a714a3c34b0c03c53c1eb0d7dcc27e04d69f42b</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ayapel</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Medio San Jorge</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:59</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>b6e59676a7da5424c8963d03c76a93d125e548bcec3e4797cd576c68d1252edc</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ayapel</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Medio San Jorge</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>02/10/2026 11:59</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>ff4b55569a69dfe25d95e57f73d1e5cadae03fb3485674c48e8cb6773caa42ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ayapel</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Medio San Jorge</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>e85fe620133184bb7c8238ee9a08fe260c38494b77098c74f68bf52c88107fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Bajo San Jorge</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>d304a220ac7239ef55a282c95f5e50127631bcf7e2e145fc5acb046c8efdf3aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bajo San Jorge</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>062c82ee5f804d7ac63e88db875dce94474649696052f2d391d44cf3350019e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Bajo San Jorge</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>d03e89bce561ffb0aa1c3372b1ba538fc9b25cd258549c3c3e539bd60557cb59</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Buenavista</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Bajo San Jorge</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>957916bd6f6bff34b278218a538ba67bc13af99ac0214119dc08a3ec29e58109</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Canalete</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Costanera 2</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>b7050f652ce8d91f823892b841294392ad222d796c4f26b24d90b3697b469a15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Canalete</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Costanera 2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>df9048a73a16650f5e310c6bcc03a587d6a3356825adbef24cbec3d56eed0294</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cerete</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>47f7bd436603967bb9dc041b0d7f44fd5be49c21c5097803e02c2087ab6b21ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cerete</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>9f1a974fbaf7afcf59699d3593b7e3c3ac1a4aad1fd9d9d730e14b9db2fb1275</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cerete</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>63dcf8cfdd07afe0f5e566a06f116ceac875a6d4a9a574ae2d9b4216b3df4459</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Cerete</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1e6cb05781c49c37bb6c9a0563467556ccb44e50a1ccb3d71d53ddc5cad8916f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chinú</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sabanas</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>dbe2f2b7dc5f154af314f9ac2ced7cb2bba36ff5ad91395dba1db9fab8f3da24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chinú</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sabanas</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:01</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>d28387d0dc66d162bd151567b36fa0fad5e052f670dc1d0a098b2b16bd42c8eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Cienaga De Oro</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>cbff34106547ccc61d69adea61da7864dda09f4011ea6b67f9b2c7327319c425</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cienaga De Oro</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>50d56fe5b08d32549650a8ca156f9a73280248d253f691616819f52c3eb963b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Cotorra</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>9157e09e77ed26fcbf5cca76cc89334207d8dd64fb290acf0230e8f71ab776d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Los Cordobas</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Costanera 2</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2ea8e4f5523e4298ca00926a3f566bae8c9bd7b48a17d1efaf3410e1a0be03c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Montelibano</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Alto San Jorge</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>4d0a8b47b8d7f0a5474d1aa207995119cba260790e02c3407b0b3ff471d37ff2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Moñitos</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Costanera 1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>6a0a3aa43798750777948401460e43b6ebc9182d919cc1095e80283a3577bfd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Bajo San Jorge</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1a8f1af85ebe71f56fafd421c47e5e60315e54b2d10512859846f9d482a7756c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Puerto Escondido</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Costanera 2</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>a934da81d6a1d92db817a1c269658329a114dea502bd4be463ab69c5ab8c5077</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>San Bernardo Del Viento</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Costanera 1</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>349d9e10e30008510ea0b9992d0072098d7645873961af8c24e4ceeb93cf1def</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>San Bernardo Del Viento</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Costanera 1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>f04ceeac6d408ab682d2ddad70985c1296bf647b7650a6e46997d15ae71a90d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>San José De Ure</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Alto San Jorge</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:02</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>ff3abfb99fc2fc82a4fb53d17290f51e548ff3d70be42a36280fab7daf87a6dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>San José De Ure</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Alto San Jorge</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2f7b5187202f2497ddf259b82ca3205f3df618b099ab8bdb203ebe7431f77f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>San Pelayo</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sinú Medio</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>512ed2bd7da6ee500f402c9c523fa0bc2c5557472fe8fa33261676a1796e2036</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tierralta</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Alto Sinú</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>a9aec0fad691691b2a1c6a02047e72b1b12dee69014b54f6766156d17fc9d35f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tierralta</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Alto Sinú</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>b8f9700785348eb91865f045faa8e8c5fafb8edf2c7dadd4c3120292d8c7c001</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tierralta</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Alto Sinú</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2ea6963615ca1e8024a78cea8697b6ff4121cd3ae1ed01f44420542d1b1b249a</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Alto Sinú</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>02/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-10-01 17:28:13</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>0e77a8238194a78effc6cd621a9ef15de9b27f7aa62a6ee6205e285a6248c870</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-10-01 17:28:13</t>
+          <t>2026-10-01 21:58:06</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5240,6 +5240,71 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>0e77a8238194a78effc6cd621a9ef15de9b27f7aa62a6ee6205e285a6248c870</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ayapel</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Medio San Jorge</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>02/10/2026 15:57</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-10-01 21:58:06</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>8e2c9671c016942b7b536e1d21cfc359fddaa901a911f6af470acea0e56a9c25</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-10-01 21:58:06</t>
+          <t>2026-10-02 01:33:03</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,591 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>La Tebaida</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Valle</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>da032c563926ab0c18ec6690cf706338810b2a3546dbf7cdd76ea9e7c0cd9337</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Quimbaya</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Valle</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>97</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>a83b1c5ebd9e6923186fc1059e4c4bd3b247a1e64dc2616653963b8e3fb3d1e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salento</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fria</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>89dca8522adc98944e557baba3211a6966834cb70a24be7d891f60ab10829632</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Leguizamo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:19</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>02dc0628c899d292ee797973ec82ebb0ddb64ab1731ff39ce777fa771dca98d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Puerto Asis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ed4c7b69f9e96da8d4c6e97de8c5124582994157f78d09e6bc735156075a84c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Medio Putumayo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8c75bbf3f33e23c50fc29727d2e8854461e7c26b34ed89fc7955dd788431f886</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Puerto Guzman</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Medio Putumayo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>84</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3412775d3cd8ab76b7681fa9d811ce843724a92bf855bbe3e6ced259cdcb2893</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Puerto Asis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>74157abd158b604cde55c17b5fe316ce59ed3f8796b5a22d57590638e52d21cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Orito</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>27</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>03/10/2026 10:20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-02 19:20:22</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>09bdd24c57225b454deb7941b08a0261b1642062b9b2f6715edfc688f7af6998</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,15 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:20:22</t>
+          <t>2026-10-02 23:10:56</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1080,6 +1080,1111 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>09bdd24c57225b454deb7941b08a0261b1642062b9b2f6715edfc688f7af6998</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:01</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>7d7d8911fe44e9d4a26a0127f162f69c418f1b86f9dde05b5fbeb6c2e8bf0e0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente tutor (Planta Temporal PTA)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:01</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>efa001f29e078c7771a30c6335b5c8d6882c80ee43aebed7e9f5ccc790676247</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cartagena Del Chairá</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cartagena del Chairá</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>875065f9f77bec2fd68df26fd833c014f358ae8a3c1204095804e9b504774091</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Curillo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Curillo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>068628d41ead77082fe7ce0f1630535f3784931e4497843bb754cf390d7dfff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Curillo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Curillo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>684d701a5b4a7294a31b50b85eebd88fe56b7f5333308f229f799cea3745c2a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>El Doncello</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>El Doncello</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>b1b5cc04337bd8acb469b5e3cb020fee1c6b29c4cac716ccb077a8cd2bbb0b8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>El Paujil</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>El Paujil</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>43fa44c1f193ff777e79e55ce97f6a40db1b7142c4f1d0083a930091c6350f49</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>La Montañita</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>La Montañita</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>af20176f83a05c02e045b98fe570ea3f4061dec732c4fba86886fe1540e68221</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>La Montañita</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>La Montañita</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>205b93ce8fe09a9a33cbf8280570bc6106071d1fa766d5edfa7751d23bb1a1fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Milán</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Milán</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>995ee86f72f8c6db372863618c8e6f0d9e0a2444681fe88211a60345872a07ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6dba03c07841e38729cc11d6d5ae5c9181a364226fe51b2c6c55d4d1df004afc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>b556bf9184ff3303599b2171b7556ff6bee9b97981ed2dd4bcda12a76c2c4903</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Vicente Del Caguan</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>San Vicente del Caguán</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>94952e8e7372aad6ac7273ede189f5c7ebdc79a2f574473bc1ea2b90b38e011e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Vicente Del Caguan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>San Vicente del Caguán</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6a1092b34e67ccfdcfdf4e93b09fce621b1199f7cc5188e520033594c8255b8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>e2443de1512cb57e90b6de2d7386a653bb7fc57c7a3ee2eb78685e504c7b7bc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Solita</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Solita</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>699b70102b8fd54e622bdd354a0af5f2f555a65006530dcf19f31dee405637a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>03/10/2026 16:03</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:10:56</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5500c6208d54f1465c9fcf737a99bc88a543ffda01dc7e9a97e6cb6de55f25a3</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-02 23:10:56</t>
+          <t>2026-10-03 01:59:13</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,2151 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dos-Vertiente Occidental</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:24</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>d8488caa32f158a430dab53fcf7f7c9723b0f770ee51e42a36e98a8b9f70a39c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Guatica</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dos-Vertiente Occidental</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>f34fcff7d83618270e41430a28f9def135e27184163244c1b0259a68b5d4b927</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1828a2a1720a5d268454f77fcdee531b5a05af5c76e9cd9b6613c6ec8417446d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>c338e457e93b7afda6ccb91fcd856037ddf007c8ced4c22740cddbb63d162cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>509e9e4a8f5f93c38f924df2bc45032d3a5193e47795d5b7213021405a62a14d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>387969e02d5175bc34f164848e07075f484881a981d611d26cd51225f651cc8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>94c180d2000df221e2720e56dc68093642ddb4ac2a512b32d03494522dbf7e74</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>35ae168399792388087046eb8cb3574da0903ebce2047f132782abefd821eb28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>59fc0597f6c60264981cbcf16545e99e83c23011761014a53e31fc6d762b4f27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>cdb3cca63692c3c6c91032da6df2265ee5acba51c102a4a673b0ee842a6ab4f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9f8f8a92cea40d2faaa8ecd1c249d976f8b1bea49a351be1b03630c0fc0b5465</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>d3cfa4b788dff0a05fd39e3a4cd1fb92c3e771fffd4e0302ba32ab8635aae874</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>e25e3854236a9ddbfad56328a5a66d48ba61f543106bcd9e4f3bc270a10b9aba</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6c6b0d68efd9f89c26380351fcc82fe27d33ee95a347bb5b11e4f36870d31052</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>f5df7400f226378b61bdeaf9f613c998a71f64a2611d4952ad1f37de2061a19e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>d5dcd9ed0e31daf655ea6b5252acd73e91e768f968508d15c69b3316dd3717c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sopetrán</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>71a4b54208cec3dbb6e1b895b89f0055aad28df52ca6eda610c19f2ed8dac831</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Santafe De Antioquia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>91edd128d23aea60e2ab6f6df392c1090d80773c725ca53726af1585b9bdb4bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>a1b218fbc68edbc3bf9277a6f27f05ab7e7d16eddae18de91d8ca014d731a43e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>f87bf0c20334bab1f78f32bfb68327aead1dc3efadc96ecface0c74f657b1ab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>602720958ac7e9bbe9ab2319b9fcff1ea424fb3adeef087ca34dd40395d6a50e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>88d021a4e146021a4829475dceb54678931a2bd2e6aa0e0e038adf40c4cc9cf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>169e420efcd3ebed9be17983cff9eb438165f4afdcd7471f79bb98dedbda0da6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>eabbfd3255d8c36ddb36d5653dd527353f8f131089f271759df28dd4be246123</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>779605e1b213ae64b378c2d3a16ccb26bca01c5d083f67da5a181f979644c70e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0846ec5ddf683f59c40adf4363d8da16062080b5597f2b4d977e017fd720346a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ea9c986680ec3b034834eaba5227d0b7c1ed9b499ca9443d8bc55fb252f2a3e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2afe64a905ed8a6419ddbf6f660d5b38ad475539774890abdc310c128255a49b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>a8228e889196692e5baf210191f19c30babecdb85fa084703906d570b123c918</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1c11af3ade7a0aec7af16475858ce8a100df659a59217dec15629a3c1bd33f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:25</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>fbdd007b1af286d8f80457df3d89f0fa63ca83242f67b64c824cbefa59868a16</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:27</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>518b50c4ec29df882a949ff0e55622a997695c09403a32345d2dc42cec9dab04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>06/10/2026 16:27</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-05 22:01:44</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>d91b54b65f4a519e10bf5ee8459b4534b8b0fc67bf27e8217cec74f29485e458</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-05 22:01:44</t>
+          <t>2026-10-06 02:18:39</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,3906 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Leguizamo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:35</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>38a0a98f08212b2c7f55f7b04f715f10b54e6e03af94fca3d10efec8c67a8c9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Puerto Asis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:35</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>585251821832b773abeb8665bc1c2915ace0e49b6dc3046829295c9575d393d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Medio Putumayo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:35</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>c28b4854c3581d2486cf443ba243e7cfe03034fd05b5fb98f2114b63fc7b0ebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Puerto Guzman</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Medio Putumayo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>c27b4ca50833f23ee52d24569419eb9c3505e980c55d0387ca9dcb89b01d565a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Puerto Asis</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:35</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4dc6e632a10701309ac513a63e0ecbe31e9fa468e0f81e5e593af267dea14f99</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Orito</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:35</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>229f311820d058867acab3e2e312644f5c1fa7dd352f75f8a872f458e1092e02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:42</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>c3f75d0f883b5639c4cab10e8f00437540f13df1fe1a7a0de0a5d40842bb4387</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aguachica</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:45</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ff7f49f53a1f3b33a1a6da312e13e28824db357d9b7d8c84e9303dc4470a5c68</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chimichagua</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:45</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>df4821ae310ede47b40e27098ec8d6179b9de1067eaa4243466abd155ba31b89</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bosconia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Noroccidental</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:45</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>a145a0a676fc700bb39254385ee20e0200bb725ff39f92d8b610416100d5c5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chimichagua</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:46</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3927b00ec8c210a6357e9e15a0bdfa351086bf42ca5d09ef7776e0f2510172bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Curumani</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:46</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>a7bfc0f31008476685e31f00c8e676133282c8d8dc8b67bdd132ef82f72f29dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chimichagua</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:46</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>a1deaf8d255c747405f37215014d5ac14490681eb7e0bf643ee25cd67817f721</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chimichagua</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:46</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>980a0e85ce1ef85d6e6232e37d9a5b260611d4369a0734e866e360089ecbbb80</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gamarra</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:46</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>df8b500e13a2e7db8bd5942c9f4f1f3d68c259b1bdf8c1133501c127c2eb73ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>El Copey</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cesár</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Noroccidental</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:46</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>fe2fd19367a10057f955a5a610ec62f9f949e4eb9be5b12677f0c1f2e608943f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>07/10/2026 09:50</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>470a0ceb23bfd17feaf47554768d2e22b71c62c16fb052dd059fae9db7514df5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>24</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>efbd8a9c7b7e50f1df66da96eec8de35d0eda566308eb403603587f35d2f2713</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>580b1384be2128ec022e808f7cbee889301488e8a6e1fa8a74e0c35687bc0331</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tunjuelito</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>97616e1770da19a738b3216b14a4f37c1fbaaec82d1b4fccee594d89c264bceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Engativa</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>81fe6c349814c847e6cd903acf5abadc33874455a1ca4eafa12688a1e098bdf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>14</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:10</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>d44018ae6119c96cdcd9610a4f5d5c6903a1b498a367134f3bad0eb9012f865f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>69589ebda2e230a3035b02a246345b087247ee4b785f16fbb60120ca280a12e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Funza</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Funza</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Funza</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>23</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>62effab7ff4192f81347b0b79e19894552d321a1f00d10d0264790437754dda6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Santa Rosalia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:14</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>d0d713ecf48265b112a4450f5d9c90eeb41b53505d6a4eed107857cb786a4e74</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cumaribo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:14</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20b88ff8706a3f4db774be3fc9e0e68a86db2670577b7597cd44bff1280d63ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:16</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>94b1e766afddfb0c0b1aa89928939088fed5031d97c0b6ec648aa6c46f23a553</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Acevedo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>21</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>606fd4fbc3c09cfd1268849163b2213f62bae01053d2475492b5ce2d9908c700</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Uno</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:17</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>039fc59794fb85220e8d9530d4f558e0957c725f587692310f50057e6667bee5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Uno</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:17</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>bedc485c7259ac38308aba5f70f7a1cf381fddcae1f1c4e2080523e3891be51a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Agustin</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:17</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>49f484c41950df2c2201d741644af85c29925611697e2da577122cdc35229f25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>eb5bd2ea1c93108b5fd3e3cc9bcf9835d36e30ead3b01c197ad645fe5d13846a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Orocue</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:19</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1d1e39e7a4dd88a9824529832b5ffdb8306a8af10e6fecf6557da78c5917e8fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Támara</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:19</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>01dfcd1db21b146cdb959f518ef93bbc5b081f9df05efda327efe6ff1cec1e13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:21</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>7483b846732e6444581729c3d62e31876892090bce7c8b99bdba2c083e776386</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dibulla</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>78ac5a507deefec359a3487b35dd8ee790f3b9c7d26339b2e4407db1439f004f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Barrancas</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1c013f850245e7f259131b26bfb68500dd4e86493c820a79c3d2431a732fa094</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Barrancas</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>4fc6083bc59922dbd673eaf855fac23e7e356c9fe92bf5c5144f5dcc893d6aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hatonuevo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>736706b99b120f0600c2ecc9c9eeb0fcf69d303d28428916b63dd95e7871c12b</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Urumita</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1c1458b25cf06b41f7eeb0e7f3bf70155e13a813414b9f308ac1f5cca9913f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dibulla</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>561e9d0187fb38af458e11e9784d830fa7be59aa256de73805280da22a30d593</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dibulla</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:22</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1c44aff7d73ee0a593023e5ec0134de9efe258afc605eea41c2d4c7fe3db22f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>San Andrés y Providencia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Andres</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>San Andrés</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>San Andrés</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:23</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3b50be09ad1535cb1e723a9035bb841b1434dce5577497b1fdee0ad15804d9ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Abrego</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Catatumbo 3</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>033e38c0c836144004eb15b1a637d5db38767afae20399883d2021d019fd5149</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Abrego</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Catatumbo 3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>975a939f557b4d32fdee857b1d7a99551adad53867c7f5058c2dc55bf35fb876</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Catatumbo 7</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>9f92082566c74ad914621bab47c32cb36499cb065d26f617cd38655d66eb4ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>El Tarra</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Catatumbo 1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>4a824b0dc0af2078e4578a4c176f6f40ec02e68b23589ea494c378cc0a399dbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>El Tarra</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Catatumbo 1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ef36607bedd6f37d1e96005b592f346ff1c77c27f7af5042087b3326a32de3f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>El Tarra</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Catatumbo 1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>e50a5b2a52753c1592fbd39d73c6ebb73e9c4fbde4547689b0e405f38d565202</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>El Tarra</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Catatumbo 1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>289b2917de8d4d0f3eb57c44d35337da64cc0a37d826f1d3acab3498c144445e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Catatumbo 9</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19f3fa460f485a369c104c690bb670e86e82c255b97c52af433e533dfb79384b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Catatumbo 9</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>9c3cfa3b6bee83a5eeaa7342b07afaaf324c79f67aa8868e6b1cc5a60d61bebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>La Esperanza</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Catatumbo 9</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>f71bbba96b6a9ef401593714c93e0e33f88e6d76f412516c0646650a12775618</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sardinata</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Catatumbo 11</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>b16c38ebcf076d51c5846b05d4c5691e50d17c3def61c2b03811c45e3071896d</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>8c80a945bdafec3324c0d43c6aacd1eca9a0ce438b0aecc97e1c8056279c297b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>579441ca3b3edd4ce1707d8985d20229dfeaa6d474570cf2f7c38b26e3da69d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tibu</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Catatumbo 6</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>b6dfba33cfecf5f0a7710920c028c5292ac85a0cdf33aebc990f85451c5ccca9</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sur Oriente</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:32</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>ec958d6fbd28f3fac24e56cfc8e535ad124b0d687ab4635d25b7e0ec04f13a5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:34</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>582adc80a1d837a0ebccdffb87cbb24158c322f1d809883cd55a67ea1f51b012</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>07/10/2026 10:35</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:09:40</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>0d2d0633bf57b24d40ac6a5a522b1ebdc94d2eb7a632d549c06886b1c66bab58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-10-06 16:09:40</t>
+          <t>2026-10-06 20:59:38</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-10-06 20:59:38</t>
+          <t>2026-10-07 00:35:47</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,396 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Usaquen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>43</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>08/10/2026 14:54</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:02:58</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5c0ff8b0d74f9196dc5ad0acb043f988f42c672b2b6db286c1fd23ef6f0db6b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Engativa</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>119</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>08/10/2026 14:54</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:02:58</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>25b03286cb109ceac300fac37871f19e40b5c51c055168c7cbcc5502e669219c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Barrios Unidos</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>31</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>08/10/2026 14:54</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:02:58</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bfa371eb7c690035ac7dae5084b6ff5856d1562e398500584a952f86fb3e8600</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Los Martires</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ciencias económicas y políticas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>88</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>08/10/2026 14:54</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:02:58</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>117ecb8a414cfebdf4bc41c501221461bfe367c78b152d71ab70ed73d9f566b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>08/10/2026 14:54</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:02:58</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1c5798e165afabbb8762635a7875226f6e29a072a29fe8e2c0759b50d5e7eff0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ciudad Bolivar</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>08/10/2026 14:54</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:02:58</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8bc6c6be22ed5d7939540b46459c59004752acacf333e8d0cc207188d496a7ed</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,396 +495,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Usaquen</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Docente Orientador</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sin asignación directa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>43</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>08/10/2026 14:54</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:02:58</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>5c0ff8b0d74f9196dc5ad0acb043f988f42c672b2b6db286c1fd23ef6f0db6b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Engativa</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Educación física, recreación y deporte</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>119</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>08/10/2026 14:54</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:02:58</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>25b03286cb109ceac300fac37871f19e40b5c51c055168c7cbcc5502e669219c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Barrios Unidos</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ciencias naturales física</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>31</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>08/10/2026 14:54</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:02:58</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bfa371eb7c690035ac7dae5084b6ff5856d1562e398500584a952f86fb3e8600</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Los Martires</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Ciencias económicas y políticas</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>88</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>08/10/2026 14:54</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:02:58</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>117ecb8a414cfebdf4bc41c501221461bfe367c78b152d71ab70ed73d9f566b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Idioma extranjero inglés</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>08/10/2026 14:54</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:02:58</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1c5798e165afabbb8762635a7875226f6e29a072a29fe8e2c0759b50d5e7eff0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ciudad Bolivar</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Idioma extranjero inglés</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>22</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>08/10/2026 14:54</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-10-08 00:02:58</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>8bc6c6be22ed5d7939540b46459c59004752acacf333e8d0cc207188d496a7ed</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,1046 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:21</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>cfdf8fcf3c5aff88afb80d47e37cf50af9c9aa18b549b1821850491bde5bb9ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bajo Occidente</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>9236b21290514a760ed015812bed50f2ae58a707070d68343f3409cdc7146402</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1e6086bcb4c81670e5e58d59412cc51a9b471595879421a000c157e5b5f3b908</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Alto Oriente</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>08577791819fd8c1b5385c0065e4c580ee0368b47293d7d1bb858311a0ca5d47</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Neira</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>55</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>48727b1bec21e7763acc61e1b88fc1ced58946277f8b60c2d290acd89d417fdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>39</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ff8b09481a8b8f26e422d277ae9757aaa1ec32e6253ee7a13d36d100dd4a76d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Viterbo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bajo Occidente</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>46</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>616e38dff80c28036c1036d89b46263e0a46b14ec792fd6bbb6c739eb4d7162f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3cea70b058f15115bcd99bdcf16bbfd3cd9601afec45d907021aea7b752dc831</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bajo Occidente</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>b8b471694ab886341bbda079e8aded8dee56dbbf6ec515527f7c0760d3c9a43e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>7d36ab2b513d84ad022fd9ed70bb74d1aed75bc5f1010b15baad27b5fd31025b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>14a02573957664b8dd9178d60c728f004da85dd0e7a585a4c144f1c119853b54</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>19</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:30</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>537f7b2ac8f0a0495e4c612e4d677e4450167d562f665afc65a8d64029bfea7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>17</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4b47d8bc6518bbdcdccbd4ee13423ad3157c92a5bf73d315428009ee274bdfc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Norte de Santander</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cucuta</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cúcuta</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>09/10/2026 11:30</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>67b07543131c5ab794aa5f081c1c829c8c0ae1fc84933f61744b5601f1a96a0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>09/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8b23ad41ad8220b57788f920a03a5659b6841e2db19a1f7c73bb8ac3773c24d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Educación artística – danzas</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>09/10/2026 12:03</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:27:57</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>8b04f9b2998a0be76f8a4e29f71c5b74e2dda0a9815bdf3bb8226daef6dac1ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>101</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-08 19:27:57</t>
+          <t>2026-10-08 23:53:32</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,136 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>61</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10/10/2026 14:52</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:39:40</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2a59d15b368275e711462faa87160689184867d52f9085c27892678ce5b91844</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10/10/2026 14:56</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:39:40</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3ca83bad517c27aeba2cd621954aa49f7a80c397d17bbaed163d5a23a7068fd9</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-09 22:39:40</t>
+          <t>2026-10-10 01:55:31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-09 22:39:40</t>
+          <t>2026-10-10 01:55:31</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,136 +495,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pasto</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Pasto</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pasto</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Preescolar</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>108</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10/10/2026 14:52</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-10 01:55:31</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2a59d15b368275e711462faa87160689184867d52f9085c27892678ce5b91844</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Valle del Cauca</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Cartago</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Cartago</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Cartago</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Educación física, recreación y deporte</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>83</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10/10/2026 14:56</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-10 01:55:31</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>3ca83bad517c27aeba2cd621954aa49f7a80c397d17bbaed163d5a23a7068fd9</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,461 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>La Vega</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Gualiva</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente Aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:38</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0fe90cd8b2ecc69c84892de34662668e30287b9d49b4cd011ae0a965d0084f87</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vergara</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Gualiva</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente Aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:38</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2c76f5b3b15abbd7cc05826869301dc063184c5c5a2cd35206b12dc5f4bba081</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pacho</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rio Negro</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:38</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6a86a1413032f9b4119f2fdff7c21f7cc6602ff96734eee88adab1f3a2749eb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paime</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Rio Negro</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente Aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>edb97e60fab3aa73adce4119736d12b0e020d074ded65059bda03209f476e648</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cabrera</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sumapaz</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente Aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:38</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>027201acf6ba08d2c3228fdc1beae3adc4156bb705a303b6411020e78cd7d567</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:44</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>320ba7c826a6686e113f734afd2655e6c61a09cbdcbad477cff5a5843b23b4a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Educación religiosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:44</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:47:03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>69f959d95e5c32b1ba42c5cbd2e16d2c7a6b2739524b3401686212381a1ac466</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -421,8 +421,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-13 20:47:03</t>
+          <t>2026-10-14 00:11:23</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -950,6 +950,1436 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>69f959d95e5c32b1ba42c5cbd2e16d2c7a6b2739524b3401686212381a1ac466</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Maripí</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>36</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:47</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>c3b793fad20f6f2b6eb1f7612dda80a58b86ce352345bf849482464975056015</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Muzo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:47</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>b7603220760ebb6f8876f4e3026da6d5209161a038eec71d99f001f515eb26b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Otanche</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>34</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>f0267bf129156dc02935e979a81b2baeb163cd9028e9ce6bac0808f891b8478d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sahagun</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sahagun</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sahagún</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>89</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>14/10/2026 15:49</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>f620d15df362c757f177cc1aa5434767a55e7d1014962cc1412bd60fd5a98ca0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1172c48d8c6e19882abc31d3fd856e35bcd89882650c59b97ea449bb2163aa53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>45</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ea34da8dd05ce2850940f41922c9b4efd11df0a88d776de5743cc6695478d02e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Balboa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Balboa</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>205ccc64b059a07686e588a680f3328bc1571eef7f69f6b33a2cc30f6aaf761b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cajibio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cajibio</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>f4782bd47a5131cc95663455706a7147bb1b11db244664045dce8067b16a4523</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Caldono</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Caldono</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>29</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>b6c6428021afdc8734fd33c14e1d59fbfd45fc1a1e0859bd5ac1bb768648735d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Inza</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Inza</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>26</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2284a6c2f23ceea2f845277d5453aab0621af7221bcedb9bc25a69a429cfb51f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mercaderes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mercaderes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0ba134f150d94fbf65ea0f6f2557a7623bdd81cfab116bf72949405a42b2e529</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Purace</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Puracé</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>b19750cc85b10442e6774fb5e17f123d473fb75e0bf5a9b609c83f9274c0cc8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Santa Rosa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Santa Rosa</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>23</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>84fc48f74989373faab2e1252bb72ef0cf89dd270bc09705b2aaa7f8179b5e03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Paez</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Paez</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>aff73fd83a41b5749ec01a4cd58c4c65ec0812f0e727b473098cd89b6fcd33b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>19</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0745f0e3d07b6ee9f761af76acb1e7f4d1d74a3293af27ec98256638ac05a50f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Piamonte</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Piamonte</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>cf21e4f3881f32f0477c72afb6599674a9adddf27c7fc7bdda386be96bf17667</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cajibio</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cajibio</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>30</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>bba0a950b6528a7eecebd3c169094e4971b8915d6459d71ecbee2f54081e3eca</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>14</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>eab152592841080f255b2f1fd9ad2beb0c727f050aa4aee35853a81acdad3aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>El Tambo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>f47dc2f4154136fe63162d9be569292218c30a2adef09f226b2089a4b3f15066</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Piamonte</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Piamonte</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5608656d31400d84fcd16e03dcb2495935b7c1ab99a1f241484cfc75179fae1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Caloto</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Caloto</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>18</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>b6af25e19847a30d645ef4b9757da5cd4485e4bbd0ecabdb06407b51fd0ff31d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>28</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>14/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:11:23</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>a3fdea61d6c30f9da095c2ad9cd459798a2b036bc57d7041db80844cab75f77b</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>89</v>
+        <v>162</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:11:23</t>
+          <t>2026-10-14 04:56:29</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,916 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Inza</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inza</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>68</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:03</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>b6ae79269df93283a37b1f38f4def188d3fd537057e14a3f8e9b5a317febfd04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>64</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>94eeb5ba1d5fcb975a14bbdcde9aafb8cefdd106133de0e9985b45e18c0fff61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9a84fdde17a80eb3aa2257d65a050a0eea50225e895de4282f624d6093a9b7d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6caae2344e7237daed90af2eaa63f5c277fbc82c66d2100b009699209b4bd0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Suroeste</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>32</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>7735f4d51d4fd36c678dd9b823f01a01c5251ab229d7f798bf406cd9db3aab05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>19</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>c52e545566d600b7586749ee4c2e2e42dc7cb010a26554ab5955fa4e631595f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>53</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>879f7704ca2f28c0fb2a7b09a203301c8954de97b68416129b781a740833a3d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>f1745be25044895b4b755a6ae43fa3fd0b63862f8ef985ce331e13dc072887b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Yondó</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>40aa3095a72f70ecdc8646a4e99d98a15abc7512228682ca364843bf81fd210b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>El Retorno</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>El Retorno</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>83683fde075119044e9916af3a78c6779ec4702d712aa3b0f0a0f41ce1e262d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Jose Del Guaviare</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>San Jose del Guaviare</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2c0fadab637031acf68e495c72658c4a7036150530a48c1c80ca7326b648febf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Santa Rosalia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>b48192837e0bd991926e8ea9ead2a83b79eae8b65b56f39b03d00d13f66f91ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cumaribo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vichada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>46</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>608620c0827a7237eb17ec4818fb72c931542e812c2c218de4b59b5d9d5645c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>84</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15/10/2026 15:40</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:48</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3506c0dde835b35cb552084a20dd3e6afb2952be26271fdee39911b03e3bde4f</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:48</t>
+          <t>2026-10-15 00:54:52</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,1566 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:07</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1d024207a50ab97f573ae006a04b6fe897f3bf4cf7bd6e220a970d54c384487a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:07</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>a4a17c89969cc1088be49ef6c699dc5913c5cd9b3551b25afd2e7a6f8a2b6c92</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1f7ed9008e43284e16b7f1ec6f83a33524b41d6150983476287714164e98779d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Inza</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inza</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:09</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ee076c281704440415f2d2c3a9d3f68774feb32d160067ce0975df3ed6520e59</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>18</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>42b1d8fa79617baf5f8c8773f029a18f0909089423fd70ba60d6c6b34b9b6842</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Leguizamo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:16</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>68bbfcfaf71582d1e47b3b82406ad1899c0d3309c7d79dc2efba222ac4b597c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Leguizamo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:16</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>65df64928035238bf8fff1073bb54886f5c22053ca99075ed5bc83e56022db00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Orito</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bajo Putumayo</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>19</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:16</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>e01d6a00c5d0b15e7edf56bb9fca3f1e19c82d2cd845a7764dea9f0aac6fd1c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Medio Putumayo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:16</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ea0ae72b04cc0fda73ece592fc6ec9d33c58f15b6034255876ebe7ec21e981a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Villagarzon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Medio Putumayo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:16</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>824a71ba73123799bee798e50ec82658c846b2acf3d34f2e45fb33fd9814ac34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:17</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9f93158e298b2b8e3a9e987ccf73e1df175cbfd3f19a4c1c6ad713198898a7e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>9bb6b6e9fc64eaa7c78d47eacf4a98332822ea159091ebb3b629bad5428f4c17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>16</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:17</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ebfc8315be187784abb5708f7ac72b4ebeb6541944fc8bb6255f381c184cc11c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Piedecuesta</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:17</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>d9d67f0eba729d8d06726de86a89049f8ad2888a111a9668e47feb47e47df81e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:19</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>099fb99aebe7350ab8f81d4569d8bd17a3d85d4880798669b09c77365d42a44a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>21</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:19</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4ae59917a0992c098f30e70fcc1f0f29c3b854d334e6dd47aece3cd03cc6cd0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>9e3215861cb5797b44a9613c46475d2aa1333aa9a176158a998429e0fbef14c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>167e1c94eb9a0b3fae264534b66f1113a9550431fbee11d6bc3714b4ca0c264b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:20</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>eaf5e1b50149b55bc2c989159de5133af512efa94aa5d51ac0eec8e52155c7e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:20</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>c7e65fcfee03621f666d6a48b3d8e4581ba217b606930ad51510e692ee35373e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>61</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>b74c2f6cccff068363eed68e13d63f7d77712e5920a1c8d14aef37c4668bb1da</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>19</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:21</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1dc0c4ac6a784487279e14acaa13f842db6d7865276816eab6e84dfc45bde2a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:23</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>662b35d83d0a5b9ae003a6210948ad255d8311272a452f43e7ae6963af925fd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>16/10/2026 16:23</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:25:51</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6a8754210d65a7fe036b94da2aa47aae88f5ee6c227d8fac77ef94898786ffe7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-15 22:25:51</t>
+          <t>2026-10-16 00:37:08</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,201 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>San Cristobal</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>212</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20/10/2026 16:11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bfa9a83f33d119cdb56f584ac91c1756bbe56a300ddb8201f9a3dbc43992d338</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bogotá D.C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Suba</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20/10/2026 16:11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>be9f9a26c248c532d83b48281bbae03d667b3db9e9497de33321ffac3f2e5cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20/10/2026 16:13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:53:08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>020cbffd1bf2e1818b9a4ad036e4d191986e215760a5096e4406544c1b73c80e</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>212</v>
+        <v>357</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-19 23:53:08</t>
+          <t>2026-10-20 03:57:07</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-19 23:53:08</t>
+          <t>2026-10-20 03:57:07</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-19 23:53:08</t>
+          <t>2026-10-20 03:57:07</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,201 +495,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>San Cristobal</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Primaria</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>357</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>20/10/2026 16:11</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-20 03:57:07</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bfa9a83f33d119cdb56f584ac91c1756bbe56a300ddb8201f9a3dbc43992d338</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bogotá D.C</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bogotá</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Suba</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Docente Orientador</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sin asignación directa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>103</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>20/10/2026 16:11</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-20 03:57:07</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>be9f9a26c248c532d83b48281bbae03d667b3db9e9497de33321ffac3f2e5cb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Valle del Cauca</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yumbo</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Yumbo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Yumbo</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Docente Orientador</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sin asignación directa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>27</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>20/10/2026 16:13</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-10-20 03:57:07</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>020cbffd1bf2e1818b9a4ad036e4d191986e215760a5096e4406544c1b73c80e</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -421,14 +421,14 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +495,396 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Soacha</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>146</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21/10/2026 13:52</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:54:20</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>b3edf27ccbd09b1fc5124a0cee200265e0460c193e1f2402f931d0000e819eda</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>28</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21/10/2026 14:00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:54:20</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>e3bf250c82d60134bd4cef446c05dd79c0f8d100c94b15c566d2adf850ec8297</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Arauquita</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Arauquita</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>21/10/2026 14:00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:54:20</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>eb4dedb79111c66fe40902c7bcb00d2fffae6e30433727642ecb2bd50af301cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>64</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21/10/2026 14:01</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:54:20</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>e3c2f6428d528aef2d986df533900e61c3f3ac88109f4843d9f9f91b7c1f5c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fortul</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fortul</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>21/10/2026 14:01</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:54:20</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>05b36311666803cfc39353c670c3fc76b7d30dd1a734f51f33fac4ab5941be66</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>42</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21/10/2026 14:01</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-20 21:54:20</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>68755eac5552c7979c3ab63ccab351520564431724905ceedd028572d568495b</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>146</v>
+        <v>274</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:20</t>
+          <t>2026-10-21 00:25:19</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:20</t>
+          <t>2026-10-21 00:25:19</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:20</t>
+          <t>2026-10-21 00:25:19</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:20</t>
+          <t>2026-10-21 00:25:19</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:20</t>
+          <t>2026-10-21 00:25:19</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:54:20</t>
+          <t>2026-10-21 00:25:19</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -421,14 +421,14 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,396 +495,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>ID Vacante (Hash)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Cundinamarca</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Soacha</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Soacha</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Soacha</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Primaria</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>274</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>21/10/2026 13:52</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-21 00:25:19</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>b3edf27ccbd09b1fc5124a0cee200265e0460c193e1f2402f931d0000e819eda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Humanidades y lengua castellana</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>43</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>21/10/2026 14:00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-21 00:25:19</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>e3bf250c82d60134bd4cef446c05dd79c0f8d100c94b15c566d2adf850ec8297</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Arauquita</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Arauquita</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Docente Orientador</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Sin asignación directa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>41</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>21/10/2026 14:00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-10-21 00:25:19</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>eb4dedb79111c66fe40902c7bcb00d2fffae6e30433727642ecb2bd50af301cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Primaria</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>21/10/2026 14:01</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-10-21 00:25:19</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>e3c2f6428d528aef2d986df533900e61c3f3ac88109f4843d9f9f91b7c1f5c37</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fortul</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fortul</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Idioma extranjero inglés</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>21/10/2026 14:01</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-10-21 00:25:19</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>05b36311666803cfc39353c670c3fc76b7d30dd1a734f51f33fac4ab5941be66</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NUEVA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tame</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tame</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Docente de aula</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Educación física, recreación y deporte</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Vacantes Generales</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>68</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>21/10/2026 14:01</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-10-21 00:25:19</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>68755eac5552c7979c3ab63ccab351520564431724905ceedd028572d568495b</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,3061 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>28d7a2813583303321fdd612c53f4b31e8a7bc2e41fe18e117c965f6a66f6202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>f6b2f44d3c90ea81f53d5979fea948320da0a0cdfd28e48fecf07511e58c3656</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>70f2375fe34051ed23b035c5566a45cd5ae87b3db9464d912a82c066c9d9e995</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>33</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>e17d88d95a5d5633118e3c49487074f506940f6fdbf6b2ca9ed30de6218b73b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Betulia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>31</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>f93226723879b3059afeb8e79184be37f23cb7b4cae23cd854208499cf2f6287</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>San Gil</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Guaneta</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>36</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>fd7fb83d17cc2e202a094f735f763a98a949b4b409449718335e731f89f4427a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Puente Nacional</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Velez</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>e89e88ca049f7d14431dc0db561b1fec1714c70704c20b183ca99ecb59166623</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rionegro</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:16</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>c0cb2f00b2d37c7503fd178543a64a01d5bfe2271abc211745e7564fa2e80ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Giron</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Girón</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Girón</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>63</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>41d7f93c1824effc17432bd9d979313f1e6573077fe697d078aa786b91755525</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Giron</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Girón</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Girón</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22/10/2026 11:20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4d1c38c3c93ef31cee7385d48a1a0eb76681b1a49c0517830785de078f9a49b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Necoclí</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>261c8478cc99c98283471c2f6ddc61dd5a0a2ff431744feffd61ef03ec32b8b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Caracolí</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Caracolí</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>67a8643e1f9140850f33fcec0217761dbd0e31660bfcffa6d812a99150e538e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>e71a056d65e439f398c9947e60b5140904c7223c573468053053a6f2462d51b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Valle del Aburrá</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>26</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>40e9313147fded22dcea26963441b3c8afce39e5bb5e7abff8bcfff637b77863</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Puerto Nare</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>e07d807f79e6fb723e76e4bda61a730d540566fb2ba3d44a9073221795a69035</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>06b61436440690c21c3d4adfa2a0c683051203cabb7e3f92f8c8e08f71b1b801</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nechí</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1b900bca2c6384717cbcd3796a4ba03ed9d2855718d25d5b1e341ebca7549fec</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Caucasia</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>af0a2cad065f903a4c5179811bea5f38aaa4b2d6ce27a9d4dc943ae2f1c6601f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1e9e95cdcc50d5a50ad837bb660e50edce8e4bd80680b55b7a5be26dc4845369</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>664812f1b4ecf78e62d3d15a633b34062cab2908c4e35adecf8f2bcc29225ebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>fea92214efef3686afc5629243c7edaf894a30f85496f8fbbcf13fb5c2516548</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>d65afb92002e8c0fc50783ec52cde26513ae5e3d466a91f425287338c957e5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>f7e9bca81200b2c624a7e08bfe19888760047ce2b6aff835942ee83858311518</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>c43ef657adb3bb9b2eff42546c107d29a1213538610d5b6a39ac2d834b0898b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:06</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>47b0c228b3bff35bc241fb8957e6f3f3c817b0f4975170a696152a37f0543525</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Anza</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>08217d862e15c0825dc65e28c68fa6f7661c30a863d3b0a9b47f95b336254be1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2217e0aeb82772fe63681ebc84ea393651aa8a17906a5794f7844e953a19f20b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Pedro De Urabá</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>San Pedro de Urabá</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>d1692fd0a64a348aff2d3d89f754b599b54421c97c4148d80d2f6f534ea711f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chigorodó</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Chigorodó</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>c44ce3bc8834f224ef0469e1038cf686c4db6bd8c1988b4f241f9624a9c89742</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>San Pedro</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>dfb7f43e680734609f53e897deff802a43f1b9cc0aa2a7af5981875ccc9a425a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6c3147d44d4b614e402b400f8b08a8f7a515d386c08f9a88d0f54c938c1d17b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Arboletes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>12</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>4b93f214070f6b34ea9e4844f3969c596a2f991c710a1ee813d31b9b35f19fd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:07</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ad004eac727af769a167c2065dd17e9a00374cb8a5f969c350d049e60478755a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:14</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>e3e5ff07de238e78ebbefe0e691fb868a8f93043a617469d96adee69baf0e0da</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Paz De Ariporo</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:15</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>3099728794208e6c8d272a909bc5e44a8fe570b87112e6755cc278e1a7c01961</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Aguazul</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:15</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>41c1fa90a222d1a0a17dd07c9b10c2aa0b0408fe189d116d6ca7cc1d89183e7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>18</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:29</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0b8fe259246c5ef5d09c0236581ccaedbabf54de54128d02e19f37f4de05f54a</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>18</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:29</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6ef6dbebd8b10d4d5a53c3db91d3fced1f4c36873fb5e3868046b97fb7ae9d73</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:40</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>cc224df36b65e37b902eab8a1a7ed70fdb8fcc534ac6f69d2b735bb0ee9fdc6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Acevedo</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>18</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2c9fbf80f8eca67b8dd953e6d31bdff38c48a2a18fb7cbc3b46a7e5663454aae</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gigante</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>f67b507ef7a7c0d19c781add2c8fb9c341a6ea29a54f6260671dc9a3e9458ecd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>16</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>bb8204435b3955802eb183e7f4bc309ba3acce3b3bb760b34b5bb99f50b93f2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Isnos</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Filosofía</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>217034d985db5f2669f7644f0c3a90cf9b86737fa76dae58deb305f43eb5a899</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>La Argentina</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Seis</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>12</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>bd460d0737e94f1d43f38c14a64205d6c6bdc945fb171492fecc54f48603be7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>San Agustin</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>25</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>cf64dac6b7e3a00d43d4faee91438e81b31fc13037d01aeaddbd88060f1a8868</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Agustin</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>13</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>69e1158f66280e3f106cb8bbd52ca3d748901b582d1cc683ade7bdf7963619ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Suaza</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>22/10/2026 13:44</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-10-21 19:29:06</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ea4267365d34b796c75871285637c31afec353b4e6385b5673a4d6de9adabdc2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-21 19:29:06</t>
+          <t>2026-10-21 22:39:36</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3550,6 +3550,71 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>ea4267365d34b796c75871285637c31afec353b4e6385b5673a4d6de9adabdc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Aranzazu</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>14</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>22/10/2026 15:36</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-10-21 22:39:36</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>e0a045d1bee873cf402c16699c47a7919bccd80ce163b991fd395e5e76d76fb1</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-21 22:39:36</t>
+          <t>2026-10-22 00:55:37</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,981 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>77</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>cd487ec4741d055ef7c0580318dbe1c0b611c83519966e2397ffb7eb453f70d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6c55bf1717bbbec0b3c76197e2d9ea08f7c4e83cab8fcb4a33fc850987512d83</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9175b18b33d03ce8aadf075296ef31714f86743d671319110e05d308eb7b9694</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:16</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0ae071d643b0de5a991701fb764626256e9be2de4b656927f1257af77a9a8f5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>39</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>960266ba3cb65752330479c16215675c99790f2f0d5ad12a9c57fda98582d020</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Palmar De Varela</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Palmar de Varela</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>06b0e98313f82b23c99e44450b07de29c4f593fafb90dbab25e21268ec609954</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:37</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>38e8637ff9a16cd3bf3109a226010418b0026ec60be7c12d76ffdefb1c60bb4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Almaguer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Almaguer</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:37</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>18216011debef45c35ed0aec8f5a18eef2eb4d1a4e296dd01f43742ed076167b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>61</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:42</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>98c714d4b5b2646545fa65e3bbc75555c6f8d5af5f45392e40eb5629b5156ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>31</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:44</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>565e3d0aabf7371eda84403e1729b04792ac95a177b0afba2274ff1eb61e6e53</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bituima</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Magdalena Centro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>fe9bfdaf00be4ddb4031d933cac69f48827a4459ca20bd920fcd3fb712a67062</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yacopi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yacopi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>80</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>831bf0d7bf8c5a45528bc58de2c19bc5070061417b00dcf1b82cecaf57692568</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Anolaima</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tequendama</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>249b8791b01430570c3f58dc8ea5789100f575fcdc3134b301a794eeaf6d661f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Simijaca</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ubate</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>45</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:45</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7d5ff4818c9af538812acdfcff0d80ce67ad6ae8ab6ca6861d780d1336f37fa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>22</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24/10/2026 12:48</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-23 20:27:32</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2b436c5927983268064fa01cb5705f5e6e5f139ce8c3a8e5384004c1a0525c5a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-23 20:27:32</t>
+          <t>2026-10-23 23:23:42</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-23 23:23:42</t>
+          <t>2026-10-24 01:51:02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,1826 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ventaquemada</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:41</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>a5b927562d22f00871f00e545f513dc0b93745961484d907aff6db0fc4df9557</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Baraya</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dos</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:42</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>f0911dce262c3f8587b5d2d128b4ec20766a1211a3cc5a65fdc9174cfb6d89e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>dc72b4c1252c67a724e454f1c52710876d04fa5e96fb703f1cc166e276018004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>9150e6f1c870780e9674f8089547dad2213b1a1b3cae48b22b7d472be9c8439d</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>c6321a7c131b2123243c251f8417af28972c0a95344aa6e4cad17dc6ca6be8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>San Martin De Loba</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>San Martín de Loba</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6add0a0c993ef2d54b77da7c4a4c460834667ec6ec38d995b6a925f3b37b0886</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Martin De Loba</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>San Martín de Loba</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>63253575439bb12b1f6ce628d9e32028a9db1df0abc475b2c0ccc7a8b2e79f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Santa Rosa Del Sur</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Santa Rosa del Sur</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>c60b2cc1f06c7398b4286c0e5f0dd5425055ac91fca798ae4ad081ee9c13cc05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Santa Rosa Del Sur</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Santa Rosa del Sur</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6aa576c21134c0dc3718d2f71e00d51cb3723b7fcd5f7355afd3c238b8685a13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Santa Rosa Del Sur</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Santa Rosa del Sur</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>64467a12e94e02cad626c77f6a1991f5af9d69176653140b71221b0613ba89a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Santa Rosa Del Sur</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Santa Rosa del Sur</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ab82e248d0007c7144cbc25cf7aadc6b0455f0885b887f4214ab7c9dfa0b958a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Santa Rosa Del Sur</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Santa Rosa del Sur</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0aba4fc4d3756b41593b4193f69c1baba3bf675ddeb86460e44fbd01e3f3be5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Arenal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Arenal</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>cdd734d156f99a55e8c78b2e509a21f1ab0e709edce3699b30ac13caac8101cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7301c282229f074dbdf04976f8cd6fd480f8109a3faf3e73c1e532925e52c0b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cantagallo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cantagallo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>30d137f60364b5e0b6a5a456c9af67bb553e0848450c91df61d3773ec0ec2af6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Altos Del Rosario</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Altos del Rosario</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>f8f8372b6d704407ee56e8a41a3ec816fba53bad058f861fcc763a33fb4a4887</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Jacinto Del Cauca</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>San Jacinto del Cauca</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>f27af06cd409e87ada7ecef2fc70b60aaf149010253455fa6aa6e947c050eb68</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Jacinto Del Cauca</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>San Jacinto del Cauca</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>7434e5b68d0daa446df6a2c9c02646b284cb948aa0d01f87ec658d1593962737</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Achí</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Achí</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5761848e973534adeaa78c618c28cc8f6e9a80000bd73ff4efff46bae9da71ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6b52d7acd6f4d70c0d3b2798e288dbde4f4ee3433339f37b85293e2f0729a0c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3e183912c7d56e5d41322952398a0bbfd6478ca20abcb8e5315b835d14e14e1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tiquisio</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>45d812ec55610c7ad7166fd98ae7ef5004ec5a923b10d700c744352450a03cc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ca4934ddf95153f26d75c68101987b2351794c2d0a79ef40e07eaba435fe8661</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>221273fd32e171e814a4ed124101d349cd149501ebe5efa292bd8447b67d9f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4e7237574a5c093f5f8e0cc33fab47ae2593e9b4ee3a11a3a12b2231d161dbb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3bf60a2088f6304ff5a70db49293d8828f7a541b6cb9007a42f43c92f63a132d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Norosí</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>a2862773e494e75808de44c87f8df96001cc9591dba75d9a82c84b1298b46659</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>27/10/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:12:40</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>66e41f67e61ecdd586ecb36af92f0b169df42369d5fc8b9b6ade51482f4ca439</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-26 21:12:40</t>
+          <t>2026-10-27 00:30:15</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2315,6 +2315,526 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>66e41f67e61ecdd586ecb36af92f0b169df42369d5fc8b9b6ade51482f4ca439</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>El Playon</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>El Playon</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>c8f1a0c9d0e66d3b031bb82bdc49522a5d15883109a241cdae52976b094576ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sabana De Torres</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>37</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1f3cb1aa9912b9287f55778714d40b88fa294758ebcd27943fcd92836444a5dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vetas</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Vetas</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>31</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>4465689592047bc15e7358822496bb0b3ad5e18f761c6c7d3f0a3457d635529e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>El Playon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>El Playon</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>7f6ff0eb56891e1122060f4015d184195e9cd286fc723da3646cc616b63e438d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Jose De Miranda</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Garcia Rovira</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Educación ética y en valores</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>19</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>5b3d2b24b29da5ef5edeaff82ded27cab49f6d5c9173c14e1d25d5661288d36d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sabana De Torres</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mares</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>3be6d2bd2f4c07ee782eb598ea17cc9b9fdccd8ca1668913bcac16f0cb4a2600</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Curiti</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Guaneta</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>22</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:18</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>9a2f05f615c2ad947b57b0b4b06fc574a4570b29dacae7a6a491e760a24f581f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Zipaquira</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Zipaquirá</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Zipaquirá</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>128</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>27/10/2026 16:20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-10-27 00:30:15</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>bc7eeeaf1d0f8cd87b275900ff5eccd338bc80568d0846895c70fbcb4d796cb1</t>
         </is>
       </c>
     </row>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,2801 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Caimito</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>San Jorge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>cc035ae5000270d5320e671388bc1366b90a2be119983193697d19f3b38a2f2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>San Luis De Since</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sabanas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>82740be471bfb69ab137c2e76c81adf08bc72715baed562ab781a603970af2f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Galeras</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sabanas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3c8096f5784fd18e802cef9dfdfab9448195b2513d91423c3f781424dbb5c274</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Guaranda</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ae0a232f96d811cd9df48ca05ccd14f194f8ffa50ed6457cc9c048be05483ad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>b4f452bb5b744194df3534d0ab27adf8431e45641934b03819ef390b88d446b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>68</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>c7b7b35608b93b9442f20c12178931adceed0998e181e9847ba2ebefd9a08f16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Idioma extranjero inglés</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>f759f9e126c5278301988abe616bfd63c28b96f3c1046808fe5a685275c1c886</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación artística - artes plásticas</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>d9fc640bbcb54f7b8d7d0bc7492c898d172d2199166a94a35694b888a93e4085</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>42</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>c8573bc980f3ab3637cf17881b999779884770c1e3198aa8332108efde063713</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4125fe854d5dcd08f1c30bc4ab7f043cf4b97d52e7adf8b6eb4c72d7980bea3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Guaranda</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Educación artística – música</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>384d128cc14c35defe903291b598db9a38cdc418dc95dfcd1e69e99c6af91f66</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Guaranda</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>27b1fdff969a6dfffd9c79038f0ea0f907e2339db61fc1386dc2192cc4d37a1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Guaranda</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>21</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>c7232e6e9cfa96063056660a607009933ccaac92c2a18ae7682f8df1abf4de22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Guaranda</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>e0c6a61e2c215066c959526b45212cd47780c526a28f5092bfed247a773420ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Guaranda</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ciencias naturales química</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>18d3344f7290ecf53315c3bb841f663f4b68c7921f6a93d0d363a6a233edd395</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>36</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>705fa94c99be3b7e269312ee8c91d78b694b45e85c3119d088d46d62ac9e72de</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>18</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6a82e1f8c54a8eff48f4867d851ec7581f2108a0be8cf2c731bb980941c829fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>b10fa9e3b35189ab627dd4a8d482d64644dfdc88d45013800fa23c8826055adc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>16</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4186a78f90893702a8d950e662082766579dd561a0eb7e100d51e6ab014a5e29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>e1d74c1e46c58c81c21061985ae6e24e22f5f3506cd3c73904f968f6e30d28d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>29855240dd4a1c4ebfa8b9673dad8d66de2a320d9350aadc473ad0e2b31468a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:17</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1177d3b75f4def78f0c0c0588bf58cc8227cf7cadaa7b2798b6841a6827f24b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Montecristo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Montecristo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6ea31cb645b4492d375f5b623274f7a7813e7be80bd8619a7b88432baf3d7fbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>aefe5858a7bf09f61aca52e135b8f0ea8d288a1066adf14746bc27c9fd108ec1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pinillos</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:20</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>553679487f41a535f8c69ee3b37f3b49dae80c4aa27022397bbea296b729f2cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2ba2da4eaefec7fbc009ff205f4f0aed57b6741edb6e8cd4136cae15a1470fea</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>48</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:22</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>4f32930e43648249570d45a4843f9fe9d223d148ecf277619854e881bdc3d978</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>19</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>d309a532619a37c97e13e2def7846b2e7110c17d30403a7ed1cafaa88084d558</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>32</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>8731a13aecad11b27438a90d2bd060c3110fe1443eda3f05dc9df29ad2afb306</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ciencias sociales</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>25</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ba42b2bab3c4e4a06eb7a0e64a421c1aae3ea1de5f97d263dbb40e76e1f5f4ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>44</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:23</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>e732e755891c43260a9604fef80a31d06e84e24cbb28c367a1e27f26a631c51a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>34</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:24</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>4b4aed3ed72d3c5ef85a9eb8d53538235d8fb2f9fd439acf51b1264186bda31d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Santo Tómas</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Santo Tómas</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>37</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>e69b6ca18b9e2284e21b0aa90d66dd7e64a04ab29a970e1f023acb63fa088622</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Patia</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Patia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>16</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>29/10/2026 15:27</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>82739151c44e997b4f77fc771adbb38114196ec771c29c8b89eb550be59b4c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>edd5976d9d1086963a1f8e7fa6863d9681e70f44ee4a119db153cd745288b90d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>1d30c655efae2a3cfca8ca4a835a8ff4085751381c6d6f3a4c18a67293cab178</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>11</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>bcc0511e79220c35f98e99eadc154e68b88f8e6a0b6366d40dbbd2a7c5fc5d89</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>13</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>cef8e765f99b386f00f8b65a940b6f9b9aab8d8bd818d923ca9f57c13967b7c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tarazá</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>21</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5e992708d899c3df4426c3175e6f02d5c7b8bac2c432642f06352c7d6d274f16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ciencias naturales y educación ambiental</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>aa92fc732b964f89ca9e3a3614efd4d6a998f9fce054b1ea5d38761955fdc447</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>28</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>845e4201a7957afd5ef2e57d3a11fa0393af91eea91d8dd5e246c9077ddf72dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Puerto Berrío</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Puerto Berrio</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9fd0527678c55b0e11cbedfecad83319dc57234cd70209fecdac13a78c726888</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>18</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>29/10/2026 16:08</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:53:23</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>bd4320f0936309bb4da814a36afcb66f497d87e1974cda3db81f73078860f15f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-28 22:53:23</t>
+          <t>2026-10-29 02:12:45</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,22 +413,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,6 +498,1826 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ciencias naturales física</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:06</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>d347145fbc3d5a02829dc46353963d5f1442232cf7f5348d14c43e70721e7ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yumbo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8112f0b1b4022cc0f5bc1a68b2027e7f4dc339d09fa3080187bcdd6ab70dbf5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Otanche</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:22</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1af15677365448aa96b953e1e865bff40bffa525f92e8247513898a127ddc3c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Baraya</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dos</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>a7f471e6eae8dcdf8b6a86935c3e86fd66ddfa5f211052ebfd6317c80eda3957</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Gigante</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cinco</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>b9d341c1f1e9670b78e4ce82a6426e0fb84b50411d246a8c5f463d87f5cb9ed4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>10c2c84a9655313e3444f241de1bf5d091adbd0c628ef49a7e95bb7c06391e7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>aef6cfa35e82d7ee38f4338521180a185d0b569a92d5f719282e274687e43683</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>7cf348a7eddd6bb5d16776536892fa552b5ea2b092aafd4e145d66a00eab8ffb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>8c781795c9a5c7bc8685d534fd1d08ade219b02fa907c5ffd02ada75d6a6531a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>35dd5956fde67e1d712036a9cafff5c549b5cec0f466e3cc7c6eb6f18a9e3969</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bf10f8875afd2d097057a4f06860b8fac96720b2da96e809b071d202a61998c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Majagual</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mojana</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tecnología e informática</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1f61714752a7bbbee86997a0b432f2ca9d67b8f1ba1b792a8046dc609a2fd803</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Fundacion</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fundación</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Educación física, recreación y deporte</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>62b9e8e5c355462b6e3e47be9819bc838ca2c92eebb93e9ea34678acbbb84a58</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remolino</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Remolino</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>a7cff4cb6f63c4a46b09104d94838faba0d43e5a7e7bcf976d3a42790e937f57</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Algarrobo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Algarrobo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>9962f3219940621c3b0c40e540b6eb1835de3e1d8f8887c33b1009e8257d59bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nueva Granada</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nueva Granada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>861189c0fc28f1f694551fb3c46e1bedd960362d621de9585ffa631c8a37c9d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ariguani</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ariguani</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>71a2cd52483cbf3bc7849b2626f6628ea9575329c0c9fb20f6a68109e7be7f02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>c2b76f1256b9469b16d3b189499aae4c3d598b1f3c0d2d189663694628ae3772</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Guamal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Guamal</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>a05590805f422c83d9a3896d0358259a9b2bfb1ddfe88296d5d69f464a5a9557</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>El Banco</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>El Banco</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>8f9b6e04b30c5bd0a71a2ac2afabd5798b19b1f4c76d56fc41ebdb720c9ddca3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Plato</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Plato</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5247c20bcd75b89bad494f15476a1ad90e7a8e9a9d57dbea435c023500a47a93</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zona Bananera</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Zona Bananera</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>071db1e227def438258408be03677504aed27cc2983b8d843224f0042436fc01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Algarrobo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Algarrobo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>9f4c857c9e4620ffaa54eabd5d294822c5a7ba8aec8d4b7e591d0a5e89ab26db</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>a49a9cea47dc3b8ca121b5ef79ea83bab505015ba5586745c84bccd2fb4bebb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Santa Barbara De Pinto</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Santa Barbara de Pinto</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Preescolar</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:34</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>f62602c7c90c8cd9395ffad0550fb495a6af283b7c9de0f5141c0caf74a1359e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Apia</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dos-Vertiente Occidental</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Humanidades y lengua castellana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:37</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5adc6a787cc543c3eebbd4a553c77cd0df531a215aae2fbcdd91dead71a6664e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Apia</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Dos-Vertiente Occidental</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:37</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>fe2f2d198e39ad22c953d69fe5021812884bd133492920d514761c2db2c44082</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Apia</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dos-Vertiente Occidental</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Docente Orientador</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sin asignación directa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Vacantes Generales</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:37</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:38:54</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>968d4ee5de47bd05ed72796a91bbcef15034307fdef46f05f887b6f108938f94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/exportaciones/historico_vacantes.xlsx
+++ b/data/exportaciones/historico_vacantes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-29 20:38:54</t>
+          <t>2026-10-30 00:25:50</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2315,6 +2315,71 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>968d4ee5de47bd05ed72796a91bbcef15034307fdef46f05f887b6f108938f94</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NUEVA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Docente de aula</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Vacantes Priorizadas para jóvenes entre 18 y 28 años</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>51</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>30/10/2026 15:39</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-10-30 00:25:50</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://sistemamaestro.mineducacion.gov.co/SistemaMaestro/busquedaVacantes.xhtml</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>994aa61e4f2cb956c665c097395561e44b18cea33cd4344846a8c64075e7c8b8</t>
         </is>
       </c>
     </row>
